--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>落下キャッチ</t>
+          <t>キャッチ・回収</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>上から落ちてくる「いいもの」を、お皿/かごで受け止める（牛乳キャッチ型）。</t>
+          <t>上から落ちてくる／降ってくるものを、エピソードの主役が受け止める・回収する。何をキャッチしどこで受けるかは、必ずエピソードの登場物から決める。</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>子を背負った親が、人混みや障害物を左右によけながらトイレ/ゴールへ走り抜ける。</t>
+          <t>主役がエピソードの舞台を進み、障害物を左右によけながらゴール（追跡対象・目的地）を目指す。追いかける・間に合わせたい系のエピソードと相性が良い。主役の乗り物・よけるもの・ゴールはすべてエピソードから決める。</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ベルトコンベアのように流れてくるものを、左右スワイプで仕分ける。</t>
+          <t>流れてくるものを左右スワイプで振り分ける。何が流れ、どこへ振り分けるかは、必ずエピソードの内容から決める。</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1問ずつ出るものを、2つの箱（食べられる/食べられない など）に振り分ける。</t>
+          <t>1問ずつ出るものを2つの箱に振り分ける。箱の意味（食べられる/食べられない など）と中身は、必ずエピソードから決める。</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>落ちてくるアイテムを、ぐらぐらの台にバランスよく積み上げる。</t>
+          <t>アイテムをぐらぐらの台に積み上げる。台とアイテムは、エピソードの小物に置き換える。</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ハプニングで開いた「穴」に、落ちてくるピースをタイミングよくはめる。</t>
+          <t>開いた穴にピースをタイミングよくはめる。穴とピースが何を指すかは、エピソードから決める。</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>裏返しのカードからペアを探す定番。</t>
+          <t>裏返しのカードからペアを探す定番型。カードの絵・ペアの意味は、必ずエピソードの登場物で置き換える。</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>出題パネルと同じ絵を、選択肢の中からすばやくタップ。</t>
+          <t>出題パネルと同じ絵を選択肢からすばやくタップ。出題内容はエピソードの場面・登場物から決める。</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>迷路の中でペアになる絵を2枚見つけると、扉が開いて進める。</t>
+          <t>迷路の中でペアになる絵を2枚見つけると扉が開く。迷路のテーマ・絵はエピソードの舞台・登場物にする。</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>お風呂,ふろ,シャワー,バス,お湯,泡,入らない</t>
+          <t>お風呂,ふろ,シャワー,バスルーム,バスタブ,お湯,泡,入らない</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1880,61 +1880,865 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>HP08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>お迎えバス・送迎ダッシュ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>バス,お迎え,送迎,園バス,遅刻,間に合,ママチャリ,自転車,幼稚園,保育園,迎え</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>幼稚園のお迎えバスをママチャリで追いかけた朝</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>バス乗り場に着いたら、お迎えバスの尾灯が見えはじめていた。ママチャリを飛ばして追いかけ、信号ごとに差が開いていく。なんとか曲がり角で追いつき、子どもは平然と「もう来ないかと思った」と言った。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>住宅街の坂道とバス通り。先を行くお迎えバスのテールランプ。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>🚌,🚲,💨,⭐</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>🚦,🚧,🐶,🚗</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🚲</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ママチャリ</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>お迎えバスをママチャリで追いかける。信号・坂・人混みをよけて距離を縮め、バスのドアまでたどり着く</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>間に合え〜!,ダーッシュ!,EMERGENCY!,しんごう…!,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ママチャリを猛烈にこぐ親。先を行くお迎えバスの後ろ姿、舞い上がる風。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HP09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>静寂の犯人探し</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>静か,静寂,米びつ,ばら撒き,ばらまき,ティッシュ,小麦粉,粉ミルク,いたずら,犯人,散らかし</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>やけに静かだと思ったら米びつ大惨事</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>洗濯物を干している間、「やけに静かだな…」。見に行くと、米びつがひっくり返され床一面にお米がばら撒かれていた。犯人はベビーチェアの上で拍手していた。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>キッチンとリビング。床一面の白いお米と、勝ち誇った顔の子ども。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>🧺,🧹,⏳,⭐</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>🍚,🐾,💨,🧦</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🧹</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ほうき</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>「やけに静かだ」の数秒間が勝負。散らかったものを時間内に集めて後片付けする回収アクション。足跡をたどる形式もよい</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ざーっ,サワサワ…,STILL…,えっ!?,しずーん</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>床一面にばら撒かれたお米の前で拍手する子ども。扉の隙間からこっそり覗く大人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HP10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>メイク&amp;化粧イタズラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>メイク,化粧,口紅,ファンデーション,ファンデ,パフ,香水,美容液,基礎化粧品,鏡</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>鏡の前のファッションショー</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>化粧をしている数分の間に、本人の顔にも母の顔にも口紅とパフが飛び火。鏡の前で完成した「作品」を、本人が自慢げに披露してくれた。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ドレッサーの前。口紅とパフの跡だらけの親子。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>💄,🪞,🎀,⭐</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>🧴,🧦,🚿,🐾</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>💄</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>口紅</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>流れてくる化粧品を正しく使う/間違えたものをよける。肌の「メイク完了度」をタイムリーに上げるパズルもよい</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>すーっ,キラキラ,完成!,WHAT!?,あらやだ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>口紅だらけの顔でドヤ顔の子どもと、口の周りだけ化粧された親。鏡の反射も活用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HP11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>スーパーおねだり大戦</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>スーパー,レジ,コンビニ,買い物,おねだり,買って,お菓子,玩具売り場,カゴ,代金</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>レジ前での大泣き一回戦</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>レジの行列で「あのお菓子買って!」が却下された瞬間、床での寝そべり大泣きが始動。周囲の視線を集めながら、最後はレジのおばちゃんが1個サービスして決着した。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>スーパーのレジ前。床で寝そべる子と小さくなる親。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>🛒,🍎,🥕,🧾</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>🍭,🧸,📢,👀</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🛒</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>買い物かご</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>流れてくるおねだりをカゴに入れる/入れると面倒になる取捨選択。周囲の視線ゲージの管理がツイスト</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>うわーん!,ほしい〜!,IGNORE…,どいて〜,ピーポー</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>床で寝そべって大泣きする子どもと、かごを持って固まる親。見守る他の客と店員。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HP12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>迷言・言い間違いアワー</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>言い間違い,迷言,名言,言えた,口癖,真似,覚え,言葉,間違い,読み間違い</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>月極駐車場は「げっきょくさん」のもの</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>駐車場を指さして「げっきょくさんのところだね」。以後、アジフライは「アジライフ」、店は「エコバッグさん」に。家族の迷言帳が1冊できあがった。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>家族の会話が飛び交うリビングや車内。フキダシの海。</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>💬,📖,⭐,✏️</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>🐦,🔇,🌀,🤖</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>フキダシ</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>出てくる言葉カードを「正しい読み方/うちの迷言」に仕分ける。迷言と絵を合わせる神経衰弱もよい</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>えっ!?,アジライフ!,あるある!,笑い声,教科書よ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>フキダシだらけで得意げに喋る子どもと、笑い転げる大人たち。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HP13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>服のこだわり大戦</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>服,着替え,お古,ボロボロ,キャラクター,自分で着,パジャマ,ズボン,靴,好きな服,着たがら</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ボロボロの服しか着ない主張</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>お古のボロボロの服を「これがいい!」と主張し、それ以外は着ない。外出先でも全身キャラクター衣装。親の服選びは毎朝の戦争である。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>朝の玄関・クローゼット前。服の山と交渉中の親子。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>👕,🧦,👗,⭐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>🥦,🌀,📢,💧</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>👕</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>服</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>流れてくる服を「本人が喜ぶ服/却下」に仕分ける。コーデ完成で得点の仕分けゲーム</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>これがいい!,ダメ!,MMM…,きらきら,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>全身キャラクター衣装でドヤ顔の子どもと、服の山に埋もれる親。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HP14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ヒヤリハット→笑い変換</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ヒヤリ,誤飲,あやうく,危ない,ぶつけ,落とし,転ん,まな板,包丁,ソファ,落下</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>まな板の包丁とそれはあまりに急で</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>料理中、隣に来た子どもがまな板の包丁に手を伸ばした。間一髪でキャッチした親の手には冷や汗。貼った「調理場立ち入り禁止テープ」は、夜には剥がされていた。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>キッチン。包丁と安全グッズが同居する戦場。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>🧤,🧲,🔒,⭐</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>🔪,🥦,💧,⚡</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🧲</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>安全マグネット</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>危険物をストップ/安全物をスルーする瞬時判定アクション。判定に迷う「迷い物」も登場。実際の安全の学びを1行添えると効果的</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>あっ!,危ない!,Phew…,セーフ!,ガーン</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>包丁に伸びる小さな手と、間一髪で止める親。コミック風の「!」マーク。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HP15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>寝相アート&amp;寝言</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>寝相,寝言,蹴っ,押しつぶし,落ちる,横転,布団,ふとん,ベッド,はみ出し</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>添い寝パパは押しつぶされる</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>添い寝で先に寝落ちしたパパが、大寝返りで子どもを押しつぶしそうになる。本人は無自覚に最高の寝相アートを描き、朝まで一切動かなかった。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>家族3人の大型ふとん。寝相アートの侵攻を示す矢印。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>🛏️,😴,🛡️,⭐</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>🌀,🦶,🥁,💤</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>防壁</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>寝相の侵攻ルートをよけきるタワーディフェンス風。ふとんの端から落ちる前に寝言を拾う形式もよい</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>どーん!,Zzz…,SNORE!,危ない!,んぁ?</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>大の字で侵攻するパパと、端っこで耐える子ども。寝相アートの軌跡を点線で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HP16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>パパあるある</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>パパ,旦那,夫,父親,お父さん,昼寝,熟睡,お菓子でつる,手抜き,本気</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>お菓子でつる父の末路</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>あやすのに疲れたパパが「お菓子あげるから」と決別のカードを切る。一時は静寂が訪れるが、以後お菓子の前でのみ要求がエスカレート。最後はママの雷が落ちた。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>リビング。お菓子の袋と、休戦協定のテーブル。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>🍪,🥤,🧸,⭐</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🥦,📢,😱,💧</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🍪</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>おやつ</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>お菓子を配って機嫌を取る配給アクション。配りすぎるとママ怒りゲージが上昇する</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ほら!,やった〜!,uh oh…,ばれた!?,ごまかす</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>お菓子の袋を高々と掲げて勝利する子どもと、げっそりしたパパ。遠くで怒るママのシルエット。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HP17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>兄弟・第二子の宿命</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>第二子,上の子,下の子,兄弟,姉妹,きょうだい,喧嘩,取り合い,妹,弟,兄,姉</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>第二子は兄への愛が重い</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>寝返りができるようになった妹が、兄のもとへハイハイで絡みに行く。兄の作品を壊すのも遊びのうち。兄は「また来た」と顔を覆うが、妹は満面の笑みである。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>リビングの絨毯。ハイハイ侵攻する妹と、砦を築く兄。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>🤝,🍼,🧸,⭐</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>🌪️,💥,📢,💧</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🧸</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>おもちゃの砦</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2人の要求を同時にさばく分身アクション。取り合いの綱引きバランスゲームもよい</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>きゃー!,あぶない!,DRAMA!,わけて!,あげる</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ハイハイで迫る赤ちゃんと、絨毯に砦を築いて守る兄。笑顔の兄妹対決。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HP18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>外出先で脱走・はぐれ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>はぐれ,迷子,店外,逃げる,脱走,外出先,走り去り,隠れ,見失</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>雑貨屋での0.5秒脱走</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>買い物中、目を離した0.5秒で店の外へ。万全の追跡態勢で路地裏を確保し、発見した場所はお店の看板猫のそば。猫と友達になっていた。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>商店街と路地裏。看板猫と並んで座る子ども。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>🐈,🤝,🧭,⭐</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>🏃,🌀,👀,📢</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🧭</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>追跡レーダー</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>視界から消えた子を追いかける追跡アクション。足跡・視線・猫の鳴き声がヒントになる</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>どこ!?,きた〜,FOUND!,やれやれ,見ーつけた</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>看板猫と仲良く並ぶ子どもを発見する親。0.5秒の脱走を示す時計。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HP19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>なんでも自分でやりたい期</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>自分で,こだわり,手伝わない,一人で,じぶんで,順番,同じで,やり直し</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>靴下は自分で履く主義</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>靴下の履き口をどうにか食い込ませ、涙目になりながらも手伝いを拒否。40分の攻防の末、左右逆のまま「じぶんで できた!」の雄叫び。親は拍手で迎えるしかない。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>玄関と靴箱の前。片方だけ妙に食い込んだ靴下。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>🧦,👍,⏳,⭐</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>🤝,📢,⏩,💧</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🧦</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>靴下</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>子どもの「自分で」を最後まで見守る根気タイムアタック。手を出すと減点の逆転ゲーム</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>じぶんで!,じっと…,みはる!,あとちょっと,STEP!?</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>逆さま靴下で「できた!」ポーズの子どもと、拍手しつつじわじわ来ている親。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>HP00</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>あるある汎用</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>玩具の海で転んだ朝</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>玩具箱をひっくり返した翌朝、そこを通り抜けようとして親が転んだ。子どもは「ぱぱ だいじょうぶ?」と笑いながら撮影を続けていた。</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>リビング。散らかった玩具の海。</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>🧸,🍼,🧦,⭐,🍱</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>🥦,💧,🌪️,🐸</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>🛒</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>かご</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>家じゅうのハプニングが飛び出す、総合あるあるゲーム</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>OOPS!,あるある!,WAAAH!,ピンチ!,WHAT!?</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>玩具の海の真ん中で高笑いする子どもと、転んだ親。</t>
         </is>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,70 +720,58 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TW05</t>
+          <t>TW06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>親子同時操作：片手は親、もう片手は子ども担当</t>
+          <t>コンボ10でオノマトペが画面を駆け巡る大演出</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TW06</t>
+          <t>TW07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>コンボ10でオノマトペが画面を駆け巡る大演出</t>
+          <t>途中から画面がくるっと回る逆さステージ（子ども目線）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TW07</t>
+          <t>TW08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>途中から画面がくるっと回る逆さステージ（子ども目線）</t>
+          <t>ラッキーアイテムを取ると一瞬スローモーション</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TW08</t>
+          <t>TW09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ラッキーアイテムを取ると一瞬スローモーション</t>
+          <t>アイテムがコミカルにバウンドする物理挙動</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TW09</t>
+          <t>TW10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
-        <is>
-          <t>アイテムがコミカルにバウンドする物理挙動</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TW10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
         <is>
           <t>連続正解でBGMのテンポがだんだん速くなる</t>
         </is>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,6 +640,28 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>事件の後でも親子が仲良く笑い合う余韻のある構図。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CD10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>無邪気顔ウォッチ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>子どもの無邪気な顔を画面の片隅（または場面内）に大きく常時表示し、状況で表情が変わる。コンボ中=にっこり、ミス=「え?」ときょとん、ピンチ=わくわく照れ顔、リザルト=ドヤ顔。親だけが必死で、子どもは無邪気——この対比が笑いの軸。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>子どもの無邪気で満面な笑顔（またはきょとん顔）を1コマの中心に大きく。親の必死な顔との対比で笑いを生む。</t>
         </is>
       </c>
     </row>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -2778,7 +2778,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2人の要求を同時にさばく分身アクション。取り合いの綱引きバランスゲームもよい</t>
+          <t>親1人で操作し、飛び込んでくる要求やハプニングをさばくアクション（子どもたちは操作せず、無邪気な顔で要求してくる側）</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_ジャンル" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_テイスト" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ_ハプニング" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作キャラ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2109,6 +2110,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>visual_guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CC01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>あわてるママ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>家事と育児の間を走り回る、よく動く頑張り屋。よろけながらも絶対あきらめない。エピソードの主役が「母・ママ」のとき最有力。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>大きな瞳と汗しずく、まとめ髪＋エプロン。4頭身のちびデフォルメ。動くときは小走りで腕をブンブン振る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CC02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>あわてるパパ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>おっちょこちょいだけど愛情は本物。勢い余ってオーバーアクションになる。エピソードの主役が「父・パパ」のとき最有力。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>逆立った髪と飛び出した目、半ズボン。4頭身のちびデフォルメ。走ると地面すれすれまで前のめり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CC03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5歳の坊や</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>自分が主人公のつもりで満面の笑み。無邪気な「主犯」。子どもがハプニング主役のエピソードのとき最有力。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>丸々としたほっぺ、ヘアゴムで跳ねるアホ毛、お気に入りのTシャツ。4頭身。はしゃぐと両手を上げて走る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CC04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>元気な女の子</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ニコニコどこでも全力。がんばる姿が輝く小さなヒロイン。子どもがハプニング主役のエピソードのとき最有力。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ツインテールが跳ねる、スカート＋レッグカバー。4頭身。喜ぶとくるっと回ってスカートがひらひら。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CC05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ちいさな赤ちゃん</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ハイハイでどこまでも進む、状況を楽しむ探検家。追いかける側・まもる側どちらのゲームでも主役にできる。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>おむつとよだれかけ、大きくてキラキラの瞳。3.5頭身。ハイハイでコトコト進み、見つけるとパチパチ拍手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CC06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ママチャリ（人物キャラの乗り物）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>子ども乗せママチャリの親子ペア。スピードが出ると目がまわるコミカルさ。移動・追跡系エピソードのとき最有力。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>前かごに花（または子どもグッズ）、荷台にリヤシート。車輪は回転アニメでコミカルに。親がペダルを必死にこぐ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CC07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ベビーカー&amp;赤ちゃん</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>押す人と乗る人のペア。段差ですっ転びそうになる瞬間が笑いどころ。お出かけ・買い物系エピソードのとき最有力。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>カゴにお買い物グッズ、日除けフード。押す親はよろけ気味、乗る赤ちゃんは寝ていても平気な顔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CC08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>うちの犬&amp;猫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ペットはキョトン顔で現場に居合わせる、動く小物（おじゃまキャラ・癒し枠）。ペットが出るエピソードや、おじゃまキャラが必要なときに使う。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>丸い体とふさふさのしっぽ。首輪と鈴。困った人のそばに正座して首をかしげる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,6 +2308,72 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>丸い体とふさふさのしっぽ。首輪と鈴。困った人のそばに正座して首をかしげる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CC09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>じいじ&amp;ばあば</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>わざと遅れて「ちょうどいい」タイミングで駆けつける、頼れる（そして時々穴な）助っ人コンビ。孫の要求には絶対勝てない。祖父母が出るエピソードのとき最有力。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>白髪に丸メガネのじいじ、結んだ髪のばあば。3.5頭身で腰がまがっているが、走ると意外と速い。孫を見つけるとまゆ毛が八の字の満面笑顔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CC10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>三輪車</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>こぎ始めの研究者（笑）、スピードは出ないが情熱は1番。小さな子の移動・追跡系エピソードのとき最有力。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>サドルの高い三輪車、バックミラー付き。前輪がフラフラして自分の意志で曲がらない。がんばってこぐ子の足が回転より速い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CC11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ハムスター</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ほっぺに全部を詰め込む、小さな逃走名手。すきまから脱走して進む。ペット・脱走・回収系エピソードや、おじゃまキャラとして使う。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>まるい体、詰まったほっぺ、小さな足。高速で回すハムスターホイール、寝床に集めた秘密の貯蔵庫。</t>
         </is>
       </c>
     </row>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30〜60秒間、出現ペースがだんだん速くなる。1プレイで勝敗が決まる。</t>
+          <t>30〜60秒間、出現ペースがどんどん速くなる。1プレイ30〜60秒でサクッと勝敗が決まる。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1問ずつ出題。30〜60秒で何問正解できるか競う。</t>
+          <t>1問ずつ出題。30〜60秒で何問正解できるか競う。テンポよく、待ち時間なし。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8組そろえるか、制限時間90秒。</t>
+          <t>6組そろえるか、制限時間60秒。待ち時間なしのテンポ重視。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8組そろえきったら成功（残り時間ボーナス）。</t>
+          <t>6組そろえきったら成功（残り時間ボーナス）。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
     </row>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_テイスト" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ_ハプニング" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作キャラ" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="江戸川区ローカル" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2110,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,6 +2135,26 @@
           <t>visual_guide</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>colors</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>face_parts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>anim</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2156,6 +2177,26 @@
           <t>大きな瞳と汗しずく、まとめ髪＋エプロン。4頭身のちびデフォルメ。動くときは小走りで腕をブンブン振る。</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>肌 #FFD9B3 / 髪 こげ茶 #5A3B2A / エプロン ピンク #FF8FAB / カーディガン クリーム #FFF3D6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>エプロン付きワンピース＋スリッポン。腰にキッチンタオル。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>まん丸の大目・ほっぺの赤み・汗しずく1〜2個・口は波線。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>待機=小刻みステップ / 移動=腕をブンブン振る小走り / 成功=ガッツポーズ / 失敗=すべって尻もち / ピンチ=目が渦巻き</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2178,6 +2219,26 @@
           <t>逆立った髪と飛び出した目、半ズボン。4頭身のちびデフォルメ。走ると地面すれすれまで前のめり。</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>肌 #FFD9B3 / 髪 黒 #2B2B33 / ポロシャツ 青 #2B50FF / 半ズボン グレー #6B7280</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ポロシャツ＋半ズボン＋サンダル。片手にスマホか鍵。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>太めの眉毛・まん丸目・鼻の点・あごの点々ひげ（任意）。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>待機=貧乏ゆすり / 移動=前のめり疾走 / 成功=バンザイ / 失敗=前転 / ピンチ=目が渦巻き</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2200,6 +2261,26 @@
           <t>丸々としたほっぺ、ヘアゴムで跳ねるアホ毛、お気に入りのTシャツ。4頭身。はしゃぐと両手を上げて走る。</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>肌 #FFE3C1 / 髪 柔らか茶 #8A5A3B / Tシャツ 黄 #FFE500 / 半ズボン 紺 #2B50FF</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>お気に入りのTシャツ＋半ズボン。背中にリュック（任意）。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ほっぺの赤み強め・大きな瞳・跳ねるアホ毛・にこにこ口。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>待機=ぴょこぴょこ / 移動=両手を上げてかっ飛び / 成功=ドヤ顔ポーズ / 失敗=大の字バウンド / ピンチ=わくわく照れ顔</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2222,6 +2303,26 @@
           <t>ツインテールが跳ねる、スカート＋レッグカバー。4頭身。喜ぶとくるっと回ってスカートがひらひら。</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>肌 #FFE3C1 / 髪 茶 #6B4226 / リボン 赤 #E8112D / スカート 赤 #E8112D / トップス 白 #FFFFFF</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>白トップス＋赤スカート＋レッグカバー。髪にリボン。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ツインテール・きらきら瞳・ほっぺの赤み。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>待機=くるっと首かしげ / 移動=スキップ / 成功=回ってポーズ / 失敗=スカートバランス / ピンチ=びっくり目</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2244,6 +2345,26 @@
           <t>おむつとよだれかけ、大きくてキラキラの瞳。3.5頭身。ハイハイでコトコト進み、見つけるとパチパチ拍手。</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>肌 #FFE8CF / 髪 薄茶（産毛）#D9B98A / おむつ 白 #FFFFFF / よだれかけ 水色 #7FD0FF</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>おむつ＋よだれかけ。手に小さなおもちゃ（任意）。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>キラキラ大目・ぷにぷにほっぺ・よだれの点。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>待機=コトコトハイハイ / 移動=高速ハイハイ / 成功=パチパチ拍手 / 失敗=ごろーん転がり / ピンチ=きょとん顔</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2266,6 +2387,26 @@
           <t>前かごに花（または子どもグッズ）、荷台にリヤシート。車輪は回転アニメでコミカルに。親がペダルを必死にこぐ。</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>フレーム 赤 #E8112D / かご・荷台 シルバー #C9C9C9 / リヤシート 紺 #2B50FF / こぐ親はCC01の色指定</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>前かごに花と野菜、荷台のリヤシートに子ども乗せ。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>回転するスポーク車輪・ハンドルに風船（任意）・こぐ足の往復。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>走行=ペダルと車輪の回転 / 減速=ブレーキのこすれる線 / 転倒=コミカルに横倒し</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2288,6 +2429,26 @@
           <t>カゴにお買い物グッズ、日除けフード。押す親はよろけ気味、乗る赤ちゃんは寝ていても平気な顔。</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ボディ 青 #2B50FF / フード 水色 #7FD0FF / カゴ ベージュ #EAD9B8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>フード付きベビーカー。カゴに買い物袋。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>大きな車輪・フードの下で寝顔の赤ちゃん・押す親の汗しずく。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>走行=ガタガタ揺れ / 段差=すっとぶ / 停止=ブレーキのカチャン</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2310,6 +2471,26 @@
           <t>丸い体とふさふさのしっぽ。首輪と鈴。困った人のそばに正座して首をかしげる。</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>犬 茶 #B5854B（レトリバー風） / 猫 白 #FFFFFF / 首輪 赤 #E8112D / 鈴 金 #FFD23F</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>首輪と鈴。犬は口に新聞紙か小物。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>犬=たれ耳・はっぱ口 / 猫=三角耳・ひげ・しっぽ。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>待機=しっぽふりふり / 移動=ダッシュ / 発見=首かしげ / おじゃま=前を横切る</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2332,6 +2513,26 @@
           <t>白髪に丸メガネのじいじ、結んだ髪のばあば。3.5頭身で腰がまがっているが、走ると意外と速い。孫を見つけるとまゆ毛が八の字の満面笑顔。</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>肌 #FFE0BE / 髪 白 #E8E8E8 / じいじ ジャケット 紺 #2B3A67 / ばあば 服 花柄ピンク #FFB6C1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>じいじ=丸メガネ＋紺ジャケット / ばあば=お団子髪＋花柄エプロン。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>じいじ=白髪・丸メガネ・口ひげ / ばあば=お団子・細い眉。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>待機=腰をさすり / 移動=意外と速い小走り / 孫発見=まゆ毛八の字の満面笑顔 / 失敗=こけそうでこけない</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2354,6 +2555,26 @@
           <t>サドルの高い三輪車、バックミラー付き。前輪がフラフラして自分の意志で曲がらない。がんばってこぐ子の足が回転より速い。</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>フレーム 赤 #E8112D / サドル 黒 #1C1C1C / ハンドルグリップ 白 #FFFFFF</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>サドル高め・バックミラー付き・ペダルにスニーカー。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>フラフラな前輪・ミラーに親の顔（小さく）・回るペダル。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>走行=がんばってこぐ足 / 曲線=自分の意志で曲がらない / 停止=フラフラ倒れる</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2374,6 +2595,26 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>まるい体、詰まったほっぺ、小さな足。高速で回すハムスターホイール、寝床に集めた秘密の貯蔵庫。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>体 金茶 #D9A45B / ほっぺ・腹 白 #FFF6E8 / 目 黒 #1C1C1C</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ほっぺにひまわりの種。寝床に紙屑の貯蔵庫。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>詰まったほっぺ・小さな手足・短い尾・はなの点。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>待機=ほっぺもぐもぐ / 移動=ホイール疾走 / 成功=ほっぺチャレンジ / 失敗=くるくる回転</t>
         </is>
       </c>
     </row>
@@ -2383,6 +2624,564 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>prompt_text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ED01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>自然・風景</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>江戸川河川敷</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>区の名前の由来でもある一級河川・江戸川と広い河川敷。土手を走るサイクリングロード。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>背景に江戸川の河川敷と土手、サイクリングロード。遠景に江戸川の流れと対岸の街並み。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>屋外・散歩・公園系エピソードの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ED02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>自然・風景</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>旧江戸川と水門</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>区を流れる旧江戸川と、至る所にある水門・堰。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>遠景に旧江戸川の水面と水門。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>水辺・河川系の舞台に</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ED03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>名所</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>葛西臨海公園</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>観覧車・水族館・BBQ広場がある区の代表公園。駅前からすぐ。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>背景に大きな観覧車と水族館のガラスドーム。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>おでかけ系エピソードの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ED04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>名所</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>小岩の菖蒲園と新小岩</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>小岩エリアの菖蒲園、新小岩駅前の商業地。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>春なら菖蒲の花畑、街の賑わいなら新小岩駅前の看板群。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>季節・街の賑わい演出に</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ED05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>名所</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>篠崎公園と区民まつり</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>広大な篠崎公園。秋の区民まつりはテントと屋台が並ぶ。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>テントと屋台が並ぶ公園の広場、幅広の広場と並木。</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>イベント・お祭り系エピソードに</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ED06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>風物詩</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>江戸川花火大会</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>毎年夏、江戸川河川敷で開催される都内最大級の花火大会。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>夜空に大きく開く花火（画面上部の演出としても使える）。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>夜・夏・お祭りの演出に</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ED07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>特産</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>小松菜</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>江戸川区特産の小松菜。名産品・郷土料理の主役。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>小松菜の束や小松菜商品を小物として登場させる。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ごはん・お買い物系エピソードの小物に</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ED08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>特産</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>江戸川佃煮</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>葛西などに老舗佃煮屋が並ぶ町。瓶詰め佃煮が名物。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>瓶詰め佃煮の棚や佃煮屋の看板。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>お買い物・スーパー系エピソードに</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ED09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>都営新宿線</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>船堀・一之江・瑞江・篠崎を走る都営新宿線。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>青い電車の側面、駅名看板（船堀/一之江/瑞江/篠崎）。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>お出かけ・送迎・ダッシュ系エピソードの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ED10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JR京葉線・総武線</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>葛西駅（京葉線）、新小岩・小岩・平井駅（総武線）。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>駅名看板と通過する電車。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>通勤・お出かけの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ED11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>街並み</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>住宅街と商店街</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>低層の戸建て住宅街、大通り沿いの商店街、自転車置き場と電柱・電線。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>戸建て住宅の並び、八百屋・クリーニング店などの小さな看板、電柱と電線。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>日常系エピソードの既定背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ED12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>街並み</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>タワーホール船堀</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>船堀駅前にある区の文化ホール。逆三角形の特徴的な塔。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>遠景に逆三角形の塔をシルエットで。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>街のランドマークとして遠景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ED13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>施設</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>江戸川区メタバース区役所</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cluster上の仮想区役所。総合案内や相談窓口が現実さながらに再現されている。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>道しるべ・案内所として「メタバース区役所」の看板を登場させる。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>メタバース会場つながりの演出に</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ED14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>公式キャラ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>エドリバー</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>江戸川区PRキャラクター。区に住むレトリバーで、頭の上に親友のきんぎょがちょこん。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>応援役・案内役として、背景や案内看板に登場させる。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>区の公式キャラクターのため使用は区の許可制。許可が取れている場合のみ登場させ、デザインを変更しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ED15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>文字・看板</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>えどがわ表記</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>看板や案内表示に使われる「えどがわ」「江戸川区」の表記。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>看板に「えどがわ」の文字。道路標識・バス停名に地区名（葛西/小岩/船堀/瑞江/篠崎/一之江）。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>看板・標識の文字として散りばめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ED16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>自然・風景</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>カルガモと花の風景</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>江戸川や旧江戸川の水面でよく見られるカルガモの親子。春は花の名所が色づく。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>遠景の水面にカルガモの親子、春の背景に花の色を添える。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>区の公式シンボルと称せず、風景モチーフとして使う</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30〜60秒間、出現ペースがどんどん速くなる。1プレイ30〜60秒でサクッと勝敗が決まる。</t>
+          <t>30〜50秒間、出現ペースがゆっくりから徐々に速くなる。1プレイ30〜50秒でサクッと勝敗が決まる。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>キャッチ+10点×コンボ。ミスでピンチゲージ+15%。</t>
+          <t>キャッチ+10点×コンボ。ミスでピンチゲージ+12%。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1問ずつ出題。30〜60秒で何問正解できるか競う。テンポよく、待ち時間なし。</t>
+          <t>1問ずつ出題。30〜50秒で何問正解できるか競う。テンポよく、待ち時間なし。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>正解+12点×コンボ。はずれでピンチゲージ+12%。</t>
+          <t>正解+12点×コンボ。はずれでピンチゲージ+10%。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -6479,17 +6479,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6組そろえるか、制限時間60秒。待ち時間なしのテンポ重視。</t>
+          <t>5組そろえるか、制限時間50秒。待ち時間なしのテンポ重視。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ペア成立+15点×コンボ。はずれでピンチゲージ+7%。</t>
+          <t>ペア成立+15点×コンボ。はずれでピンチゲージ+6%。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6組そろえきったら成功（残り時間ボーナス）。</t>
+          <t>5組そろえきったら成功（残り時間ボーナス）。</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
     </row>

--- a/happening_db.xlsx
+++ b/happening_db.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アーケード型" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ゲームテンプレート" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ゲーム内仕掛け" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コメディ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ツイスト" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="バリエーション" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_イラスト" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_ジャンル" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_テイスト" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ_ハプニング" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作キャラ" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="江戸川区ローカル" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="エピソード素材" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ゲームテンプレート" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ゲーム内仕掛け" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コメディ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ツイスト" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="バリエーション" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_イラスト" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_ジャンル" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パターン_テイスト" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ_ハプニング" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作キャラ" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="江戸川区ローカル" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,1398 +706,136 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>style_text</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sample_title</t>
+          <t>palette_text</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sample_episode</t>
+          <t>font_text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>scene_hook</t>
+          <t>bg_text</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>good_items</t>
+          <t>effect_text</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>bad_items</t>
+          <t>bgm_text</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>player_label</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>game_hook</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>onomatopoe</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>illust_idea</t>
+          <t>se_text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HP01</t>
+          <t>T_POP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>牛乳・飲み物こぼれ</t>
+          <t>アメコミPOP風</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>牛乳,ミルク,こぼし,こぼれ,ジュース,水,コップ,麦茶,コーヒー</t>
+          <t>ベンデイドット・ハーフトーン網点を背景・オブジェクトに適用。太い黒フチ(solid 3px〜5px)、強烈なコントラスト、高彩度の配色。レトロコミック・ヴィンテージ印刷風の質感や枠線。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>牛乳を全部こぼされた朝</t>
+          <t>シアン #00C2FF / ビビッドイエロー #FFE500 / クリムゾンレッド #E8112D / ホワイト #FFFFFF / インクブラック #141414</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>洗濯物を干しに行った隙に、リビングで子どもが牛乳パックを両手で握りつぶしていた。床も壁も、犬まで牛乳まみれだった。</t>
+          <t>丸ゴシック系の太字(例: 'M PLUS Rounded 1c','Hiragino Maru Gothic ProN','Yu Gothic')。タイトルは少し傾けて配置。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>朝のリビング。床に広がる白い水たまりと、倒れた牛乳パック。</t>
+          <t>ハーフトーン網点(ドットパターン)の背景 + 紙のような温かい地色</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>🥛,🍼,🧃,☕</t>
+          <t>ギザギザのコミック風フキダシ(OOPS!/EMERGENCY!/WHAT!?/CATCH!)が画面に飛び出す演出。ヒット・ピンチ時の画面全体シェイク、スターバースト衝撃線、星・汗・水滴のパーティクル放出。コンボ・重要イベント時に一瞬のヒットストップ(数フレーム)とズーム。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🥦,🧦,💧</t>
+          <t>レトロファンク風のベースライン+アルペジオメロディのアップテンポBGM(128bpm相当)を、Web Audio APIのタイマー/シーケンサーで自動演奏。START操作時にAudioContextを安全に初期化・アンミュートして即時再生。タイトル画面とリザルト画面はジングル/BGMを切り替え。画面内にBGMのON/OFFトグルを設置。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>🍽️</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>お皿</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>こぼれる前の飲み物をお皿で受け止める / 床の水たまりをすばやくふき取る</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ざっぱーん!,OOPS!,MY GOD!,ヌルヌル…,WAAAH!</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>倒れた牛乳パックから飛び散る牛乳。驚いて両手を広げる親と、なぜか得意げな子ども。</t>
+          <t>成功音=小気味よいピッチ上昇・ファンファーレ / 失敗・衝突音=濁ったノイズ+ピッチ下降 / 警告音=ピンチゲージ80%以上でのリズミカルな警報アラート / アクション音=ボタンクリック、スライド、ダッシュ。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HP02</t>
+          <t>T_PIXEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>トイレダッシュ</t>
+          <t>16ビットドットスタイル</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>トイレ,うんち,うんこ,おしっこ,おまる,漏らす</t>
+          <t>16ビット時代のドット絵グラフィック。チェッカー状のピクセルパターン背景。滑らかなグラデーションを避け、ピクセル感を保つ。レトロ家庭用ゲーム機風のベゼル枠。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>トイレまであと300メートル</t>
+          <t>レトログリーン #3EE6C1 / ミッドナイトブルー #101828 / サンイエロー #FFD23F / コーラルピンク #FF5D8F / ホワイト #F4F4F4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>商店街で「うんち!」が宣言された。迷路みたいな路地、避けきれない人混み、そして最後の一本道。親子の全力ダッシュ3分間。</t>
+          <t>ピクセル/等幅フォント(例: 'Courier New', monospace)。8bit風タイポ。数字は桁を揃える。</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>人混みと路地。視線の先に光るトイレのピクトグラム。</t>
+          <t>ピクセルパターン背景 + CRT風の走査線(任意)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🧻,🚽,💧,⭐</t>
+          <t>8bit風の爆発エフェクト(ピクセル粒子・星型スプライト)。画面シェイク、ヒットストップ、コンボ時ズーム。フキダシは角ばった8bit風の枠(OOPS!/EMERGENCY!/WHAT!?)。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>🚧,🌀,🦠</t>
+          <t>チップチューン風BGM(150bpm相当・スクエアウェーブ中心)をWeb Audio APIでシーケンサー自動演奏。START操作時にAudioContextを安全に初期化。タイトル/リザルトでジングル切替。BGM ON/OFFトグルを設置。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🧑</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>親(子を背負い)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>「うんち!」と言い出した子を背負って、人混みをよけながらトイレへダッシュ</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>EMERGENCY!,うんち!,ダーッシュ!,まにあえ〜!,WHAT!?</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>子を背負って全力疾走する親。後ろに青白いオーラ、前方に光るトイレサイン。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HP03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ごはん大乱戦</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ごはん,ご飯,食,食べ,たべ,離乳食,野菜,夕食,朝食,おやつ,パン,ランチ,口</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>夕食が床に消えていく</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ごはんを口に運ぶたび、いらないものが床に落ちていく。終わってみれば、床に落ちた量のほうが多かった日があった。</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>食卓の上。飛び散るごはん粒と野菜。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>🍚,🥕,🍎,🍜</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>🧦,🪀,📱</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>👅</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>おくち</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>口に運べる食べものと、食べちゃいけないものを見分けてキャッチする</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>あーん!,もぐもぐ,べっぴょ!!,UHHH…,もういや!</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>食卓でスプーンを高くかざす子ども。飛び散るごはん粒と野菜、後ろで固まる親。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HP04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>おひるね大作戦</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>寝ない,寝た,お昼寝,おひるね,寝かしつけ,眠,ねむ,夜泣き,寝返り,添い寝,おねんね</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>絵本3冊でも寝なかった夜</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3冊の絵本と子守唄をフル投入したが、本人は最後までお目々ぱっちり。眠りに落ちたのは、添い寝した親のほうだった。</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>薄暗い寝室。ふとんの上、頭上に月光とZの文字。</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>😴,🌙,🧸,⭐</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>🥁,📢,🔔</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>🛏️</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ふとん</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>眠くなるアイテムを集めて子どもを寝かしつける / うるさい音をよけて夢をまもる</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Zzz…,ねむい…,SHHH!,んぁ?,まだねない!</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ふとんで熟睡する子どもと、隣で身動きできない親。頭上にZの文字と月光。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HP05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>らくがき大作戦</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>落書き,らくがき,描い,かいた,クレヨン,絵の具,ペン,壁に描</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>壁に家族の似顔絵美術館</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>トイレに行って戻ると、白い壁にクレヨンで「家族全員の似顔絵」が完成していた。犬には、しっかり首輪まで描かれていた。</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>白い壁や畳に広がる、カラフルで大胆な落書き。</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>🖍️,🎨,⭐,🌸</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>🧦,🍕,💧</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>🧽</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>スポンジ</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>壁を走る落書きをスポンジで消す / いい絵と消しちゃいけない絵を見分ける</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>描いちゃった!,WHAT!?,最高傑作!,ピカソ!?,うわー!</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>壁いっぱいの「作品」の前でドヤ顔の子ども。後ろで言葉を失う親。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HP06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>お風呂大爆発</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>お風呂,ふろ,シャワー,バスルーム,バスタブ,お湯,泡,入らない</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>お風呂から脱走忍者</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>お風呂の湯船に、パジャマのまま飛び込もうとして抱き止めた。その2秒後、泡だらけの姿で脱走を開始した。</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>バスルーム。床までこぼれる泡と、湯船の縁。</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>🛁,🧼,🦆,⭐</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>🧦,📱,🪣</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>🪣</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>おけ</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>泡を集めてお風呂を完成させる / 脱走する子をよけいながら洗い上げる</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>じゃぶじゃぶ!,ぶくぶく,入らない〜!,SHHH!,WAAAH!</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>泡まみれで風船みたいにふくらんだ子ども。バスタブからこぼれ落ちる泡。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HP07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>スマホとり合い</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>スマホ,携帯,スマフォ,アイフォン,電話,充電,動画</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>正座でにらむスマホ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>スマホで動画を見ていたら、画面の前で誰かが直立不動の正座を始めた。じりじりと距離を詰めてくるその手を、止められない。</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>リビングのソファ。画面の前で正座する子どもの影。</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>📱,🔋,⭐,🎧</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>🧸,🍕,💧</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>📱</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>スマホ</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>子どもの手からスマホをまもる / とられないようにすばやくスワイプ</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>じーっ,取り返した!,NOOO!,ぎゃー,WHAT!?</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>スマホを高くかかげる親と、飛びつく子ども。静止画なのに動きが伝わる構図。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HP08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>お迎えバス・送迎ダッシュ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>バス,お迎え,送迎,園バス,遅刻,間に合,ママチャリ,自転車,幼稚園,保育園,迎え</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>幼稚園のお迎えバスをママチャリで追いかけた朝</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>バス乗り場に着いたら、お迎えバスの尾灯が見えはじめていた。ママチャリを飛ばして追いかけ、信号ごとに差が開いていく。なんとか曲がり角で追いつき、子どもは平然と「もう来ないかと思った」と言った。</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>住宅街の坂道とバス通り。先を行くお迎えバスのテールランプ。</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>🚌,🚲,💨,⭐</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>🚦,🚧,🐶,🚗</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🚲</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ママチャリ</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>お迎えバスをママチャリで追いかける。信号・坂・人混みをよけて距離を縮め、バスのドアまでたどり着く</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>間に合え〜!,ダーッシュ!,EMERGENCY!,しんごう…!,WHAT!?</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ママチャリを猛烈にこぐ親。先を行くお迎えバスの後ろ姿、舞い上がる風。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HP09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>静寂の犯人探し</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>静か,静寂,米びつ,ばら撒き,ばらまき,ティッシュ,小麦粉,粉ミルク,いたずら,犯人,散らかし</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>やけに静かだと思ったら米びつ大惨事</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>洗濯物を干している間、「やけに静かだな…」。見に行くと、米びつがひっくり返され床一面にお米がばら撒かれていた。犯人はベビーチェアの上で拍手していた。</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>キッチンとリビング。床一面の白いお米と、勝ち誇った顔の子ども。</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>🧺,🧹,⏳,⭐</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>🍚,🐾,💨,🧦</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🧹</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ほうき</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>「やけに静かだ」の数秒間が勝負。散らかったものを時間内に集めて後片付けする回収アクション。足跡をたどる形式もよい</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ざーっ,サワサワ…,STILL…,えっ!?,しずーん</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>床一面にばら撒かれたお米の前で拍手する子ども。扉の隙間からこっそり覗く大人。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HP10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>メイク&amp;化粧イタズラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>メイク,化粧,口紅,ファンデーション,ファンデ,パフ,香水,美容液,基礎化粧品,鏡</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>鏡の前のファッションショー</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>化粧をしている数分の間に、本人の顔にも母の顔にも口紅とパフが飛び火。鏡の前で完成した「作品」を、本人が自慢げに披露してくれた。</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ドレッサーの前。口紅とパフの跡だらけの親子。</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>💄,🪞,🎀,⭐</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>🧴,🧦,🚿,🐾</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>💄</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>口紅</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>流れてくる化粧品を正しく使う/間違えたものをよける。肌の「メイク完了度」をタイムリーに上げるパズルもよい</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>すーっ,キラキラ,完成!,WHAT!?,あらやだ</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>口紅だらけの顔でドヤ顔の子どもと、口の周りだけ化粧された親。鏡の反射も活用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HP11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>スーパーおねだり大戦</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>スーパー,レジ,コンビニ,買い物,おねだり,買って,お菓子,玩具売り場,カゴ,代金</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>レジ前での大泣き一回戦</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>レジの行列で「あのお菓子買って!」が却下された瞬間、床での寝そべり大泣きが始動。周囲の視線を集めながら、最後はレジのおばちゃんが1個サービスして決着した。</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>スーパーのレジ前。床で寝そべる子と小さくなる親。</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>🛒,🍎,🥕,🧾</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>🍭,🧸,📢,👀</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>🛒</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>買い物かご</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>流れてくるおねだりをカゴに入れる/入れると面倒になる取捨選択。周囲の視線ゲージの管理がツイスト</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>うわーん!,ほしい〜!,IGNORE…,どいて〜,ピーポー</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>床で寝そべって大泣きする子どもと、かごを持って固まる親。見守る他の客と店員。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HP12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>迷言・言い間違いアワー</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>言い間違い,迷言,名言,言えた,口癖,真似,覚え,言葉,間違い,読み間違い</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>月極駐車場は「げっきょくさん」のもの</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>駐車場を指さして「げっきょくさんのところだね」。以後、アジフライは「アジライフ」、店は「エコバッグさん」に。家族の迷言帳が1冊できあがった。</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>家族の会話が飛び交うリビングや車内。フキダシの海。</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>💬,📖,⭐,✏️</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>🐦,🔇,🌀,🤖</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>💬</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>フキダシ</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>出てくる言葉カードを「正しい読み方/うちの迷言」に仕分ける。迷言と絵を合わせる神経衰弱もよい</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>えっ!?,アジライフ!,あるある!,笑い声,教科書よ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>フキダシだらけで得意げに喋る子どもと、笑い転げる大人たち。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HP13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>服のこだわり大戦</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>服,着替え,お古,ボロボロ,キャラクター,自分で着,パジャマ,ズボン,靴,好きな服,着たがら</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ボロボロの服しか着ない主張</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>お古のボロボロの服を「これがいい!」と主張し、それ以外は着ない。外出先でも全身キャラクター衣装。親の服選びは毎朝の戦争である。</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>朝の玄関・クローゼット前。服の山と交渉中の親子。</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>👕,🧦,👗,⭐</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>🥦,🌀,📢,💧</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>👕</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>服</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>流れてくる服を「本人が喜ぶ服/却下」に仕分ける。コーデ完成で得点の仕分けゲーム</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>これがいい!,ダメ!,MMM…,きらきら,WHAT!?</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>全身キャラクター衣装でドヤ顔の子どもと、服の山に埋もれる親。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>HP14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ヒヤリハット→笑い変換</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ヒヤリ,誤飲,あやうく,危ない,ぶつけ,落とし,転ん,まな板,包丁,ソファ,落下</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>まな板の包丁とそれはあまりに急で</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>料理中、隣に来た子どもがまな板の包丁に手を伸ばした。間一髪でキャッチした親の手には冷や汗。貼った「調理場立ち入り禁止テープ」は、夜には剥がされていた。</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>キッチン。包丁と安全グッズが同居する戦場。</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>🧤,🧲,🔒,⭐</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>🔪,🥦,💧,⚡</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>🧲</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>安全マグネット</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>危険物をストップ/安全物をスルーする瞬時判定アクション。判定に迷う「迷い物」も登場。実際の安全の学びを1行添えると効果的</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>あっ!,危ない!,Phew…,セーフ!,ガーン</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>包丁に伸びる小さな手と、間一髪で止める親。コミック風の「!」マーク。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HP15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>寝相アート&amp;寝言</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>寝相,寝言,蹴っ,押しつぶし,落ちる,横転,布団,ふとん,ベッド,はみ出し</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>添い寝パパは押しつぶされる</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>添い寝で先に寝落ちしたパパが、大寝返りで子どもを押しつぶしそうになる。本人は無自覚に最高の寝相アートを描き、朝まで一切動かなかった。</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>家族3人の大型ふとん。寝相アートの侵攻を示す矢印。</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>🛏️,😴,🛡️,⭐</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>🌀,🦶,🥁,💤</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🛡️</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>防壁</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>寝相の侵攻ルートをよけきるタワーディフェンス風。ふとんの端から落ちる前に寝言を拾う形式もよい</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>どーん!,Zzz…,SNORE!,危ない!,んぁ?</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>大の字で侵攻するパパと、端っこで耐える子ども。寝相アートの軌跡を点線で。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HP16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>パパあるある</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>パパ,旦那,夫,父親,お父さん,昼寝,熟睡,お菓子でつる,手抜き,本気</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>お菓子でつる父の末路</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>あやすのに疲れたパパが「お菓子あげるから」と決別のカードを切る。一時は静寂が訪れるが、以後お菓子の前でのみ要求がエスカレート。最後はママの雷が落ちた。</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>リビング。お菓子の袋と、休戦協定のテーブル。</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>🍪,🥤,🧸,⭐</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>🥦,📢,😱,💧</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🍪</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>おやつ</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>お菓子を配って機嫌を取る配給アクション。配りすぎるとママ怒りゲージが上昇する</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>ほら!,やった〜!,uh oh…,ばれた!?,ごまかす</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>お菓子の袋を高々と掲げて勝利する子どもと、げっそりしたパパ。遠くで怒るママのシルエット。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HP17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>兄弟・第二子の宿命</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>第二子,上の子,下の子,兄弟,姉妹,きょうだい,喧嘩,取り合い,妹,弟,兄,姉</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>第二子は兄への愛が重い</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>寝返りができるようになった妹が、兄のもとへハイハイで絡みに行く。兄の作品を壊すのも遊びのうち。兄は「また来た」と顔を覆うが、妹は満面の笑みである。</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>リビングの絨毯。ハイハイ侵攻する妹と、砦を築く兄。</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>🤝,🍼,🧸,⭐</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>🌪️,💥,📢,💧</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🧸</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>おもちゃの砦</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>親1人で操作し、飛び込んでくる要求やハプニングをさばくアクション（子どもたちは操作せず、無邪気な顔で要求してくる側）</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>きゃー!,あぶない!,DRAMA!,わけて!,あげる</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ハイハイで迫る赤ちゃんと、絨毯に砦を築いて守る兄。笑顔の兄妹対決。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>HP18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>外出先で脱走・はぐれ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>はぐれ,迷子,店外,逃げる,脱走,外出先,走り去り,隠れ,見失</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>雑貨屋での0.5秒脱走</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>買い物中、目を離した0.5秒で店の外へ。万全の追跡態勢で路地裏を確保し、発見した場所はお店の看板猫のそば。猫と友達になっていた。</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>商店街と路地裏。看板猫と並んで座る子ども。</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>🐈,🤝,🧭,⭐</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>🏃,🌀,👀,📢</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🧭</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>追跡レーダー</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>視界から消えた子を追いかける追跡アクション。足跡・視線・猫の鳴き声がヒントになる</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>どこ!?,きた〜,FOUND!,やれやれ,見ーつけた</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>看板猫と仲良く並ぶ子どもを発見する親。0.5秒の脱走を示す時計。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>HP19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>なんでも自分でやりたい期</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>自分で,こだわり,手伝わない,一人で,じぶんで,順番,同じで,やり直し</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>靴下は自分で履く主義</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>靴下の履き口をどうにか食い込ませ、涙目になりながらも手伝いを拒否。40分の攻防の末、左右逆のまま「じぶんで できた!」の雄叫び。親は拍手で迎えるしかない。</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>玄関と靴箱の前。片方だけ妙に食い込んだ靴下。</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>🧦,👍,⏳,⭐</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>🤝,📢,⏩,💧</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🧦</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>靴下</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>子どもの「自分で」を最後まで見守る根気タイムアタック。手を出すと減点の逆転ゲーム</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>じぶんで!,じっと…,みはる!,あとちょっと,STEP!?</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>逆さま靴下で「できた!」ポーズの子どもと、拍手しつつじわじわ来ている親。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HP00</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>あるある汎用</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>玩具の海で転んだ朝</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>玩具箱をひっくり返した翌朝、そこを通り抜けようとして親が転んだ。子どもは「ぱぱ だいじょうぶ?」と笑いながら撮影を続けていた。</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>リビング。散らかった玩具の海。</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>🧸,🍼,🧦,⭐,🍱</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>🥦,💧,🌪️,🐸</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🛒</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>かご</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>家じゅうのハプニングが飛び出す、総合あるあるゲーム</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>OOPS!,あるある!,WAAAH!,ピンチ!,WHAT!?</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>玩具の海の真ん中で高笑いする子どもと、転んだ親。</t>
+          <t>成功音=上昇アルペジオ / 失敗音=下降ノイズ / 警告音=警報ビープ / アクション音=ブリップ音。</t>
         </is>
       </c>
     </row>
@@ -2111,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2122,499 +861,1398 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>visual_guide</t>
+          <t>sample_title</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>colors</t>
+          <t>sample_episode</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>outfit</t>
+          <t>scene_hook</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>face_parts</t>
+          <t>good_items</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>anim</t>
+          <t>bad_items</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_label</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>game_hook</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>onomatopoe</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>illust_idea</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CC01</t>
+          <t>HP01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>あわてるママ</t>
+          <t>牛乳・飲み物こぼれ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>家事と育児の間を走り回る、よく動く頑張り屋。よろけながらも絶対あきらめない。エピソードの主役が「母・ママ」のとき最有力。</t>
+          <t>牛乳,ミルク,こぼし,こぼれ,ジュース,水,コップ,麦茶,コーヒー</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>大きな瞳と汗しずく、まとめ髪＋エプロン。4頭身のちびデフォルメ。動くときは小走りで腕をブンブン振る。</t>
+          <t>牛乳を全部こぼされた朝</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>肌 #FFD9B3 / 髪 こげ茶 #5A3B2A / エプロン ピンク #FF8FAB / カーディガン クリーム #FFF3D6</t>
+          <t>洗濯物を干しに行った隙に、リビングで子どもが牛乳パックを両手で握りつぶしていた。床も壁も、犬まで牛乳まみれだった。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>エプロン付きワンピース＋スリッポン。腰にキッチンタオル。</t>
+          <t>朝のリビング。床に広がる白い水たまりと、倒れた牛乳パック。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>まん丸の大目・ほっぺの赤み・汗しずく1〜2個・口は波線。</t>
+          <t>🥛,🍼,🧃,☕</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>待機=小刻みステップ / 移動=腕をブンブン振る小走り / 成功=ガッツポーズ / 失敗=すべって尻もち / ピンチ=目が渦巻き</t>
+          <t>🥦,🧦,💧</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🍽️</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>お皿</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>こぼれる前の飲み物をお皿で受け止める / 床の水たまりをすばやくふき取る</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ざっぱーん!,OOPS!,MY GOD!,ヌルヌル…,WAAAH!</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>倒れた牛乳パックから飛び散る牛乳。驚いて両手を広げる親と、なぜか得意げな子ども。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CC02</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>あわてるパパ</t>
+          <t>トイレダッシュ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>おっちょこちょいだけど愛情は本物。勢い余ってオーバーアクションになる。エピソードの主役が「父・パパ」のとき最有力。</t>
+          <t>トイレ,うんち,うんこ,おしっこ,おまる,漏らす</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>逆立った髪と飛び出した目、半ズボン。4頭身のちびデフォルメ。走ると地面すれすれまで前のめり。</t>
+          <t>トイレまであと300メートル</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>肌 #FFD9B3 / 髪 黒 #2B2B33 / ポロシャツ 青 #2B50FF / 半ズボン グレー #6B7280</t>
+          <t>商店街で「うんち!」が宣言された。迷路みたいな路地、避けきれない人混み、そして最後の一本道。親子の全力ダッシュ3分間。</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ポロシャツ＋半ズボン＋サンダル。片手にスマホか鍵。</t>
+          <t>人混みと路地。視線の先に光るトイレのピクトグラム。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>太めの眉毛・まん丸目・鼻の点・あごの点々ひげ（任意）。</t>
+          <t>🧻,🚽,💧,⭐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>待機=貧乏ゆすり / 移動=前のめり疾走 / 成功=バンザイ / 失敗=前転 / ピンチ=目が渦巻き</t>
+          <t>🚧,🌀,🦠</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🧑</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>親(子を背負い)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>「うんち!」と言い出した子を背負って、人混みをよけながらトイレへダッシュ</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>EMERGENCY!,うんち!,ダーッシュ!,まにあえ〜!,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>子を背負って全力疾走する親。後ろに青白いオーラ、前方に光るトイレサイン。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CC03</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5歳の坊や</t>
+          <t>ごはん大乱戦</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>自分が主人公のつもりで満面の笑み。無邪気な「主犯」。子どもがハプニング主役のエピソードのとき最有力。</t>
+          <t>ごはん,ご飯,食,食べ,たべ,離乳食,野菜,夕食,朝食,おやつ,パン,ランチ,口</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丸々としたほっぺ、ヘアゴムで跳ねるアホ毛、お気に入りのTシャツ。4頭身。はしゃぐと両手を上げて走る。</t>
+          <t>夕食が床に消えていく</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>肌 #FFE3C1 / 髪 柔らか茶 #8A5A3B / Tシャツ 黄 #FFE500 / 半ズボン 紺 #2B50FF</t>
+          <t>ごはんを口に運ぶたび、いらないものが床に落ちていく。終わってみれば、床に落ちた量のほうが多かった日があった。</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>お気に入りのTシャツ＋半ズボン。背中にリュック（任意）。</t>
+          <t>食卓の上。飛び散るごはん粒と野菜。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ほっぺの赤み強め・大きな瞳・跳ねるアホ毛・にこにこ口。</t>
+          <t>🍚,🥕,🍎,🍜</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>待機=ぴょこぴょこ / 移動=両手を上げてかっ飛び / 成功=ドヤ顔ポーズ / 失敗=大の字バウンド / ピンチ=わくわく照れ顔</t>
+          <t>🧦,🪀,📱</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>👅</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>おくち</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>口に運べる食べものと、食べちゃいけないものを見分けてキャッチする</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>あーん!,もぐもぐ,べっぴょ!!,UHHH…,もういや!</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>食卓でスプーンを高くかざす子ども。飛び散るごはん粒と野菜、後ろで固まる親。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC04</t>
+          <t>HP04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>元気な女の子</t>
+          <t>おひるね大作戦</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ニコニコどこでも全力。がんばる姿が輝く小さなヒロイン。子どもがハプニング主役のエピソードのとき最有力。</t>
+          <t>寝ない,寝た,お昼寝,おひるね,寝かしつけ,眠,ねむ,夜泣き,寝返り,添い寝,おねんね</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ツインテールが跳ねる、スカート＋レッグカバー。4頭身。喜ぶとくるっと回ってスカートがひらひら。</t>
+          <t>絵本3冊でも寝なかった夜</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>肌 #FFE3C1 / 髪 茶 #6B4226 / リボン 赤 #E8112D / スカート 赤 #E8112D / トップス 白 #FFFFFF</t>
+          <t>3冊の絵本と子守唄をフル投入したが、本人は最後までお目々ぱっちり。眠りに落ちたのは、添い寝した親のほうだった。</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>白トップス＋赤スカート＋レッグカバー。髪にリボン。</t>
+          <t>薄暗い寝室。ふとんの上、頭上に月光とZの文字。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ツインテール・きらきら瞳・ほっぺの赤み。</t>
+          <t>😴,🌙,🧸,⭐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>待機=くるっと首かしげ / 移動=スキップ / 成功=回ってポーズ / 失敗=スカートバランス / ピンチ=びっくり目</t>
+          <t>🥁,📢,🔔</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🛏️</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ふとん</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>眠くなるアイテムを集めて子どもを寝かしつける / うるさい音をよけて夢をまもる</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Zzz…,ねむい…,SHHH!,んぁ?,まだねない!</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ふとんで熟睡する子どもと、隣で身動きできない親。頭上にZの文字と月光。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC05</t>
+          <t>HP05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ちいさな赤ちゃん</t>
+          <t>らくがき大作戦</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ハイハイでどこまでも進む、状況を楽しむ探検家。追いかける側・まもる側どちらのゲームでも主役にできる。</t>
+          <t>落書き,らくがき,描い,かいた,クレヨン,絵の具,ペン,壁に描</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>おむつとよだれかけ、大きくてキラキラの瞳。3.5頭身。ハイハイでコトコト進み、見つけるとパチパチ拍手。</t>
+          <t>壁に家族の似顔絵美術館</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>肌 #FFE8CF / 髪 薄茶（産毛）#D9B98A / おむつ 白 #FFFFFF / よだれかけ 水色 #7FD0FF</t>
+          <t>トイレに行って戻ると、白い壁にクレヨンで「家族全員の似顔絵」が完成していた。犬には、しっかり首輪まで描かれていた。</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>おむつ＋よだれかけ。手に小さなおもちゃ（任意）。</t>
+          <t>白い壁や畳に広がる、カラフルで大胆な落書き。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>キラキラ大目・ぷにぷにほっぺ・よだれの点。</t>
+          <t>🖍️,🎨,⭐,🌸</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>待機=コトコトハイハイ / 移動=高速ハイハイ / 成功=パチパチ拍手 / 失敗=ごろーん転がり / ピンチ=きょとん顔</t>
+          <t>🧦,🍕,💧</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🧽</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>スポンジ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>壁を走る落書きをスポンジで消す / いい絵と消しちゃいけない絵を見分ける</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>描いちゃった!,WHAT!?,最高傑作!,ピカソ!?,うわー!</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>壁いっぱいの「作品」の前でドヤ顔の子ども。後ろで言葉を失う親。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC06</t>
+          <t>HP06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ママチャリ（人物キャラの乗り物）</t>
+          <t>お風呂大爆発</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>子ども乗せママチャリの親子ペア。スピードが出ると目がまわるコミカルさ。移動・追跡系エピソードのとき最有力。</t>
+          <t>お風呂,ふろ,シャワー,バスルーム,バスタブ,お湯,泡,入らない</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>前かごに花（または子どもグッズ）、荷台にリヤシート。車輪は回転アニメでコミカルに。親がペダルを必死にこぐ。</t>
+          <t>お風呂から脱走忍者</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>フレーム 赤 #E8112D / かご・荷台 シルバー #C9C9C9 / リヤシート 紺 #2B50FF / こぐ親はCC01の色指定</t>
+          <t>お風呂の湯船に、パジャマのまま飛び込もうとして抱き止めた。その2秒後、泡だらけの姿で脱走を開始した。</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>前かごに花と野菜、荷台のリヤシートに子ども乗せ。</t>
+          <t>バスルーム。床までこぼれる泡と、湯船の縁。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>回転するスポーク車輪・ハンドルに風船（任意）・こぐ足の往復。</t>
+          <t>🛁,🧼,🦆,⭐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>走行=ペダルと車輪の回転 / 減速=ブレーキのこすれる線 / 転倒=コミカルに横倒し</t>
+          <t>🧦,📱,🪣</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🪣</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>おけ</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>泡を集めてお風呂を完成させる / 脱走する子をよけいながら洗い上げる</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>じゃぶじゃぶ!,ぶくぶく,入らない〜!,SHHH!,WAAAH!</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>泡まみれで風船みたいにふくらんだ子ども。バスタブからこぼれ落ちる泡。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC07</t>
+          <t>HP07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ベビーカー&amp;赤ちゃん</t>
+          <t>スマホとり合い</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>押す人と乗る人のペア。段差ですっ転びそうになる瞬間が笑いどころ。お出かけ・買い物系エピソードのとき最有力。</t>
+          <t>スマホ,携帯,スマフォ,アイフォン,電話,充電,動画</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>カゴにお買い物グッズ、日除けフード。押す親はよろけ気味、乗る赤ちゃんは寝ていても平気な顔。</t>
+          <t>正座でにらむスマホ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ボディ 青 #2B50FF / フード 水色 #7FD0FF / カゴ ベージュ #EAD9B8</t>
+          <t>スマホで動画を見ていたら、画面の前で誰かが直立不動の正座を始めた。じりじりと距離を詰めてくるその手を、止められない。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>フード付きベビーカー。カゴに買い物袋。</t>
+          <t>リビングのソファ。画面の前で正座する子どもの影。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>大きな車輪・フードの下で寝顔の赤ちゃん・押す親の汗しずく。</t>
+          <t>📱,🔋,⭐,🎧</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>走行=ガタガタ揺れ / 段差=すっとぶ / 停止=ブレーキのカチャン</t>
+          <t>🧸,🍕,💧</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>📱</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>スマホ</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>子どもの手からスマホをまもる / とられないようにすばやくスワイプ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>じーっ,取り返した!,NOOO!,ぎゃー,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>スマホを高くかかげる親と、飛びつく子ども。静止画なのに動きが伝わる構図。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CC08</t>
+          <t>HP08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>うちの犬&amp;猫</t>
+          <t>お迎えバス・送迎ダッシュ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ペットはキョトン顔で現場に居合わせる、動く小物（おじゃまキャラ・癒し枠）。ペットが出るエピソードや、おじゃまキャラが必要なときに使う。</t>
+          <t>バス,お迎え,送迎,園バス,遅刻,間に合,ママチャリ,自転車,幼稚園,保育園,迎え</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>丸い体とふさふさのしっぽ。首輪と鈴。困った人のそばに正座して首をかしげる。</t>
+          <t>幼稚園のお迎えバスをママチャリで追いかけた朝</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>犬 茶 #B5854B（レトリバー風） / 猫 白 #FFFFFF / 首輪 赤 #E8112D / 鈴 金 #FFD23F</t>
+          <t>バス乗り場に着いたら、お迎えバスの尾灯が見えはじめていた。ママチャリを飛ばして追いかけ、信号ごとに差が開いていく。なんとか曲がり角で追いつき、子どもは平然と「もう来ないかと思った」と言った。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>首輪と鈴。犬は口に新聞紙か小物。</t>
+          <t>住宅街の坂道とバス通り。先を行くお迎えバスのテールランプ。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>犬=たれ耳・はっぱ口 / 猫=三角耳・ひげ・しっぽ。</t>
+          <t>🚌,🚲,💨,⭐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>待機=しっぽふりふり / 移動=ダッシュ / 発見=首かしげ / おじゃま=前を横切る</t>
+          <t>🚦,🚧,🐶,🚗</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🚲</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ママチャリ</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>お迎えバスをママチャリで追いかける。信号・坂・人混みをよけて距離を縮め、バスのドアまでたどり着く</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>間に合え〜!,ダーッシュ!,EMERGENCY!,しんごう…!,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ママチャリを猛烈にこぐ親。先を行くお迎えバスの後ろ姿、舞い上がる風。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CC09</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>じいじ&amp;ばあば</t>
+          <t>静寂の犯人探し</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>わざと遅れて「ちょうどいい」タイミングで駆けつける、頼れる（そして時々穴な）助っ人コンビ。孫の要求には絶対勝てない。祖父母が出るエピソードのとき最有力。</t>
+          <t>静か,静寂,米びつ,ばら撒き,ばらまき,ティッシュ,小麦粉,粉ミルク,いたずら,犯人,散らかし</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>白髪に丸メガネのじいじ、結んだ髪のばあば。3.5頭身で腰がまがっているが、走ると意外と速い。孫を見つけるとまゆ毛が八の字の満面笑顔。</t>
+          <t>やけに静かだと思ったら米びつ大惨事</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>肌 #FFE0BE / 髪 白 #E8E8E8 / じいじ ジャケット 紺 #2B3A67 / ばあば 服 花柄ピンク #FFB6C1</t>
+          <t>洗濯物を干している間、「やけに静かだな…」。見に行くと、米びつがひっくり返され床一面にお米がばら撒かれていた。犯人はベビーチェアの上で拍手していた。</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>じいじ=丸メガネ＋紺ジャケット / ばあば=お団子髪＋花柄エプロン。</t>
+          <t>キッチンとリビング。床一面の白いお米と、勝ち誇った顔の子ども。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>じいじ=白髪・丸メガネ・口ひげ / ばあば=お団子・細い眉。</t>
+          <t>🧺,🧹,⏳,⭐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>待機=腰をさすり / 移動=意外と速い小走り / 孫発見=まゆ毛八の字の満面笑顔 / 失敗=こけそうでこけない</t>
+          <t>🍚,🐾,💨,🧦</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🧹</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ほうき</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>「やけに静かだ」の数秒間が勝負。散らかったものを時間内に集めて後片付けする回収アクション。足跡をたどる形式もよい</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ざーっ,サワサワ…,STILL…,えっ!?,しずーん</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>床一面にばら撒かれたお米の前で拍手する子ども。扉の隙間からこっそり覗く大人。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CC10</t>
+          <t>HP10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>三輪車</t>
+          <t>メイク&amp;化粧イタズラ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>こぎ始めの研究者（笑）、スピードは出ないが情熱は1番。小さな子の移動・追跡系エピソードのとき最有力。</t>
+          <t>メイク,化粧,口紅,ファンデーション,ファンデ,パフ,香水,美容液,基礎化粧品,鏡</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>サドルの高い三輪車、バックミラー付き。前輪がフラフラして自分の意志で曲がらない。がんばってこぐ子の足が回転より速い。</t>
+          <t>鏡の前のファッションショー</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>フレーム 赤 #E8112D / サドル 黒 #1C1C1C / ハンドルグリップ 白 #FFFFFF</t>
+          <t>化粧をしている数分の間に、本人の顔にも母の顔にも口紅とパフが飛び火。鏡の前で完成した「作品」を、本人が自慢げに披露してくれた。</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>サドル高め・バックミラー付き・ペダルにスニーカー。</t>
+          <t>ドレッサーの前。口紅とパフの跡だらけの親子。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>フラフラな前輪・ミラーに親の顔（小さく）・回るペダル。</t>
+          <t>💄,🪞,🎀,⭐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>走行=がんばってこぐ足 / 曲線=自分の意志で曲がらない / 停止=フラフラ倒れる</t>
+          <t>🧴,🧦,🚿,🐾</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>💄</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>口紅</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>流れてくる化粧品を正しく使う/間違えたものをよける。肌の「メイク完了度」をタイムリーに上げるパズルもよい</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>すーっ,キラキラ,完成!,WHAT!?,あらやだ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>口紅だらけの顔でドヤ顔の子どもと、口の周りだけ化粧された親。鏡の反射も活用。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CC11</t>
+          <t>HP11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ハムスター</t>
+          <t>スーパーおねだり大戦</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ほっぺに全部を詰め込む、小さな逃走名手。すきまから脱走して進む。ペット・脱走・回収系エピソードや、おじゃまキャラとして使う。</t>
+          <t>スーパー,レジ,コンビニ,買い物,おねだり,買って,お菓子,玩具売り場,カゴ,代金</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>まるい体、詰まったほっぺ、小さな足。高速で回すハムスターホイール、寝床に集めた秘密の貯蔵庫。</t>
+          <t>レジ前での大泣き一回戦</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>体 金茶 #D9A45B / ほっぺ・腹 白 #FFF6E8 / 目 黒 #1C1C1C</t>
+          <t>レジの行列で「あのお菓子買って!」が却下された瞬間、床での寝そべり大泣きが始動。周囲の視線を集めながら、最後はレジのおばちゃんが1個サービスして決着した。</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ほっぺにひまわりの種。寝床に紙屑の貯蔵庫。</t>
+          <t>スーパーのレジ前。床で寝そべる子と小さくなる親。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>詰まったほっぺ・小さな手足・短い尾・はなの点。</t>
+          <t>🛒,🍎,🥕,🧾</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>待機=ほっぺもぐもぐ / 移動=ホイール疾走 / 成功=ほっぺチャレンジ / 失敗=くるくる回転</t>
+          <t>🍭,🧸,📢,👀</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🛒</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>買い物かご</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>流れてくるおねだりをカゴに入れる/入れると面倒になる取捨選択。周囲の視線ゲージの管理がツイスト</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>うわーん!,ほしい〜!,IGNORE…,どいて〜,ピーポー</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>床で寝そべって大泣きする子どもと、かごを持って固まる親。見守る他の客と店員。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HP12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>迷言・言い間違いアワー</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>言い間違い,迷言,名言,言えた,口癖,真似,覚え,言葉,間違い,読み間違い</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>月極駐車場は「げっきょくさん」のもの</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>駐車場を指さして「げっきょくさんのところだね」。以後、アジフライは「アジライフ」、店は「エコバッグさん」に。家族の迷言帳が1冊できあがった。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>家族の会話が飛び交うリビングや車内。フキダシの海。</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>💬,📖,⭐,✏️</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>🐦,🔇,🌀,🤖</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>フキダシ</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>出てくる言葉カードを「正しい読み方/うちの迷言」に仕分ける。迷言と絵を合わせる神経衰弱もよい</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>えっ!?,アジライフ!,あるある!,笑い声,教科書よ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>フキダシだらけで得意げに喋る子どもと、笑い転げる大人たち。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HP13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>服のこだわり大戦</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>服,着替え,お古,ボロボロ,キャラクター,自分で着,パジャマ,ズボン,靴,好きな服,着たがら</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ボロボロの服しか着ない主張</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>お古のボロボロの服を「これがいい!」と主張し、それ以外は着ない。外出先でも全身キャラクター衣装。親の服選びは毎朝の戦争である。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>朝の玄関・クローゼット前。服の山と交渉中の親子。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>👕,🧦,👗,⭐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>🥦,🌀,📢,💧</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>👕</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>服</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>流れてくる服を「本人が喜ぶ服/却下」に仕分ける。コーデ完成で得点の仕分けゲーム</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>これがいい!,ダメ!,MMM…,きらきら,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>全身キャラクター衣装でドヤ顔の子どもと、服の山に埋もれる親。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HP14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ヒヤリハット→笑い変換</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ヒヤリ,誤飲,あやうく,危ない,ぶつけ,落とし,転ん,まな板,包丁,ソファ,落下</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>まな板の包丁とそれはあまりに急で</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>料理中、隣に来た子どもがまな板の包丁に手を伸ばした。間一髪でキャッチした親の手には冷や汗。貼った「調理場立ち入り禁止テープ」は、夜には剥がされていた。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>キッチン。包丁と安全グッズが同居する戦場。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>🧤,🧲,🔒,⭐</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>🔪,🥦,💧,⚡</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🧲</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>安全マグネット</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>危険物をストップ/安全物をスルーする瞬時判定アクション。判定に迷う「迷い物」も登場。実際の安全の学びを1行添えると効果的</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>あっ!,危ない!,Phew…,セーフ!,ガーン</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>包丁に伸びる小さな手と、間一髪で止める親。コミック風の「!」マーク。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HP15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>寝相アート&amp;寝言</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>寝相,寝言,蹴っ,押しつぶし,落ちる,横転,布団,ふとん,ベッド,はみ出し</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>添い寝パパは押しつぶされる</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>添い寝で先に寝落ちしたパパが、大寝返りで子どもを押しつぶしそうになる。本人は無自覚に最高の寝相アートを描き、朝まで一切動かなかった。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>家族3人の大型ふとん。寝相アートの侵攻を示す矢印。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>🛏️,😴,🛡️,⭐</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>🌀,🦶,🥁,💤</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🛡️</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>防壁</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>寝相の侵攻ルートをよけきるタワーディフェンス風。ふとんの端から落ちる前に寝言を拾う形式もよい</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>どーん!,Zzz…,SNORE!,危ない!,んぁ?</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>大の字で侵攻するパパと、端っこで耐える子ども。寝相アートの軌跡を点線で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HP16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>パパあるある</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>パパ,旦那,夫,父親,お父さん,昼寝,熟睡,お菓子でつる,手抜き,本気</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>お菓子でつる父の末路</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>あやすのに疲れたパパが「お菓子あげるから」と決別のカードを切る。一時は静寂が訪れるが、以後お菓子の前でのみ要求がエスカレート。最後はママの雷が落ちた。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>リビング。お菓子の袋と、休戦協定のテーブル。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>🍪,🥤,🧸,⭐</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🥦,📢,😱,💧</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🍪</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>おやつ</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>お菓子を配って機嫌を取る配給アクション。配りすぎるとママ怒りゲージが上昇する</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ほら!,やった〜!,uh oh…,ばれた!?,ごまかす</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>お菓子の袋を高々と掲げて勝利する子どもと、げっそりしたパパ。遠くで怒るママのシルエット。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HP17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>兄弟・第二子の宿命</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>第二子,上の子,下の子,兄弟,姉妹,きょうだい,喧嘩,取り合い,妹,弟,兄,姉</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>第二子は兄への愛が重い</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>寝返りができるようになった妹が、兄のもとへハイハイで絡みに行く。兄の作品を壊すのも遊びのうち。兄は「また来た」と顔を覆うが、妹は満面の笑みである。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>リビングの絨毯。ハイハイ侵攻する妹と、砦を築く兄。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>🤝,🍼,🧸,⭐</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>🌪️,💥,📢,💧</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🧸</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>おもちゃの砦</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>親1人で操作し、飛び込んでくる要求やハプニングをさばくアクション（子どもたちは操作せず、無邪気な顔で要求してくる側）</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>きゃー!,あぶない!,DRAMA!,わけて!,あげる</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ハイハイで迫る赤ちゃんと、絨毯に砦を築いて守る兄。笑顔の兄妹対決。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HP18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>外出先で脱走・はぐれ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>はぐれ,迷子,店外,逃げる,脱走,外出先,走り去り,隠れ,見失</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>雑貨屋での0.5秒脱走</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>買い物中、目を離した0.5秒で店の外へ。万全の追跡態勢で路地裏を確保し、発見した場所はお店の看板猫のそば。猫と友達になっていた。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>商店街と路地裏。看板猫と並んで座る子ども。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>🐈,🤝,🧭,⭐</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>🏃,🌀,👀,📢</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🧭</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>追跡レーダー</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>視界から消えた子を追いかける追跡アクション。足跡・視線・猫の鳴き声がヒントになる</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>どこ!?,きた〜,FOUND!,やれやれ,見ーつけた</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>看板猫と仲良く並ぶ子どもを発見する親。0.5秒の脱走を示す時計。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HP19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>なんでも自分でやりたい期</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>自分で,こだわり,手伝わない,一人で,じぶんで,順番,同じで,やり直し</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>靴下は自分で履く主義</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>靴下の履き口をどうにか食い込ませ、涙目になりながらも手伝いを拒否。40分の攻防の末、左右逆のまま「じぶんで できた!」の雄叫び。親は拍手で迎えるしかない。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>玄関と靴箱の前。片方だけ妙に食い込んだ靴下。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>🧦,👍,⏳,⭐</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>🤝,📢,⏩,💧</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🧦</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>靴下</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>子どもの「自分で」を最後まで見守る根気タイムアタック。手を出すと減点の逆転ゲーム</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>じぶんで!,じっと…,みはる!,あとちょっと,STEP!?</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>逆さま靴下で「できた!」ポーズの子どもと、拍手しつつじわじわ来ている親。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HP00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>あるある汎用</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>玩具の海で転んだ朝</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>玩具箱をひっくり返した翌朝、そこを通り抜けようとして親が転んだ。子どもは「ぱぱ だいじょうぶ?」と笑いながら撮影を続けていた。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>リビング。散らかった玩具の海。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>🧸,🍼,🧦,⭐,🍱</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>🥦,💧,🌪️,🐸</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🛒</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>かご</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>家じゅうのハプニングが飛び出す、総合あるあるゲーム</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OOPS!,あるある!,WAAAH!,ピンチ!,WHAT!?</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>玩具の海の真ん中で高笑いする子どもと、転んだ親。</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2640,539 +2278,499 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>visual_guide</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>prompt_text</t>
+          <t>colors</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>face_parts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>anim</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ED01</t>
+          <t>CC01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>自然・風景</t>
+          <t>あわてるママ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>江戸川河川敷</t>
+          <t>家事と育児の間を走り回る、よく動く頑張り屋。よろけながらも絶対あきらめない。エピソードの主役が「母・ママ」のとき最有力。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>区の名前の由来でもある一級河川・江戸川と広い河川敷。土手を走るサイクリングロード。</t>
+          <t>大きな瞳と汗しずく、まとめ髪＋エプロン。4頭身のちびデフォルメ。動くときは小走りで腕をブンブン振る。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>背景に江戸川の河川敷と土手、サイクリングロード。遠景に江戸川の流れと対岸の街並み。</t>
+          <t>肌 #FFD9B3 / 髪 こげ茶 #5A3B2A / エプロン ピンク #FF8FAB / カーディガン クリーム #FFF3D6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>屋外・散歩・公園系エピソードの背景に</t>
+          <t>エプロン付きワンピース＋スリッポン。腰にキッチンタオル。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>まん丸の大目・ほっぺの赤み・汗しずく1〜2個・口は波線。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>待機=小刻みステップ / 移動=腕をブンブン振る小走り / 成功=ガッツポーズ / 失敗=すべって尻もち / ピンチ=目が渦巻き</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ED02</t>
+          <t>CC02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>自然・風景</t>
+          <t>あわてるパパ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>旧江戸川と水門</t>
+          <t>おっちょこちょいだけど愛情は本物。勢い余ってオーバーアクションになる。エピソードの主役が「父・パパ」のとき最有力。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>区を流れる旧江戸川と、至る所にある水門・堰。</t>
+          <t>逆立った髪と飛び出した目、半ズボン。4頭身のちびデフォルメ。走ると地面すれすれまで前のめり。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>遠景に旧江戸川の水面と水門。</t>
+          <t>肌 #FFD9B3 / 髪 黒 #2B2B33 / ポロシャツ 青 #2B50FF / 半ズボン グレー #6B7280</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>水辺・河川系の舞台に</t>
+          <t>ポロシャツ＋半ズボン＋サンダル。片手にスマホか鍵。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>太めの眉毛・まん丸目・鼻の点・あごの点々ひげ（任意）。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>待機=貧乏ゆすり / 移動=前のめり疾走 / 成功=バンザイ / 失敗=前転 / ピンチ=目が渦巻き</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ED03</t>
+          <t>CC03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>名所</t>
+          <t>5歳の坊や</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>葛西臨海公園</t>
+          <t>自分が主人公のつもりで満面の笑み。無邪気な「主犯」。子どもがハプニング主役のエピソードのとき最有力。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>観覧車・水族館・BBQ広場がある区の代表公園。駅前からすぐ。</t>
+          <t>丸々としたほっぺ、ヘアゴムで跳ねるアホ毛、お気に入りのTシャツ。4頭身。はしゃぐと両手を上げて走る。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>背景に大きな観覧車と水族館のガラスドーム。</t>
+          <t>肌 #FFE3C1 / 髪 柔らか茶 #8A5A3B / Tシャツ 黄 #FFE500 / 半ズボン 紺 #2B50FF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>おでかけ系エピソードの背景に</t>
+          <t>お気に入りのTシャツ＋半ズボン。背中にリュック（任意）。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ほっぺの赤み強め・大きな瞳・跳ねるアホ毛・にこにこ口。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>待機=ぴょこぴょこ / 移動=両手を上げてかっ飛び / 成功=ドヤ顔ポーズ / 失敗=大の字バウンド / ピンチ=わくわく照れ顔</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ED04</t>
+          <t>CC04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>名所</t>
+          <t>元気な女の子</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>小岩の菖蒲園と新小岩</t>
+          <t>ニコニコどこでも全力。がんばる姿が輝く小さなヒロイン。子どもがハプニング主役のエピソードのとき最有力。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>小岩エリアの菖蒲園、新小岩駅前の商業地。</t>
+          <t>ツインテールが跳ねる、スカート＋レッグカバー。4頭身。喜ぶとくるっと回ってスカートがひらひら。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>春なら菖蒲の花畑、街の賑わいなら新小岩駅前の看板群。</t>
+          <t>肌 #FFE3C1 / 髪 茶 #6B4226 / リボン 赤 #E8112D / スカート 赤 #E8112D / トップス 白 #FFFFFF</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>季節・街の賑わい演出に</t>
+          <t>白トップス＋赤スカート＋レッグカバー。髪にリボン。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ツインテール・きらきら瞳・ほっぺの赤み。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>待機=くるっと首かしげ / 移動=スキップ / 成功=回ってポーズ / 失敗=スカートバランス / ピンチ=びっくり目</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ED05</t>
+          <t>CC05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>名所</t>
+          <t>ちいさな赤ちゃん</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>篠崎公園と区民まつり</t>
+          <t>ハイハイでどこまでも進む、状況を楽しむ探検家。追いかける側・まもる側どちらのゲームでも主役にできる。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>広大な篠崎公園。秋の区民まつりはテントと屋台が並ぶ。</t>
+          <t>おむつとよだれかけ、大きくてキラキラの瞳。3.5頭身。ハイハイでコトコト進み、見つけるとパチパチ拍手。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>テントと屋台が並ぶ公園の広場、幅広の広場と並木。</t>
+          <t>肌 #FFE8CF / 髪 薄茶（産毛）#D9B98A / おむつ 白 #FFFFFF / よだれかけ 水色 #7FD0FF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>イベント・お祭り系エピソードに</t>
+          <t>おむつ＋よだれかけ。手に小さなおもちゃ（任意）。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>キラキラ大目・ぷにぷにほっぺ・よだれの点。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>待機=コトコトハイハイ / 移動=高速ハイハイ / 成功=パチパチ拍手 / 失敗=ごろーん転がり / ピンチ=きょとん顔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ED06</t>
+          <t>CC06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>風物詩</t>
+          <t>ママチャリ（人物キャラの乗り物）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>江戸川花火大会</t>
+          <t>子ども乗せママチャリの親子ペア。スピードが出ると目がまわるコミカルさ。移動・追跡系エピソードのとき最有力。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>毎年夏、江戸川河川敷で開催される都内最大級の花火大会。</t>
+          <t>前かごに花（または子どもグッズ）、荷台にリヤシート。車輪は回転アニメでコミカルに。親がペダルを必死にこぐ。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>夜空に大きく開く花火（画面上部の演出としても使える）。</t>
+          <t>フレーム 赤 #E8112D / かご・荷台 シルバー #C9C9C9 / リヤシート 紺 #2B50FF / こぐ親はCC01の色指定</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>夜・夏・お祭りの演出に</t>
+          <t>前かごに花と野菜、荷台のリヤシートに子ども乗せ。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>回転するスポーク車輪・ハンドルに風船（任意）・こぐ足の往復。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>走行=ペダルと車輪の回転 / 減速=ブレーキのこすれる線 / 転倒=コミカルに横倒し</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ED07</t>
+          <t>CC07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>特産</t>
+          <t>ベビーカー&amp;赤ちゃん</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>小松菜</t>
+          <t>押す人と乗る人のペア。段差ですっ転びそうになる瞬間が笑いどころ。お出かけ・買い物系エピソードのとき最有力。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>江戸川区特産の小松菜。名産品・郷土料理の主役。</t>
+          <t>カゴにお買い物グッズ、日除けフード。押す親はよろけ気味、乗る赤ちゃんは寝ていても平気な顔。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>小松菜の束や小松菜商品を小物として登場させる。</t>
+          <t>ボディ 青 #2B50FF / フード 水色 #7FD0FF / カゴ ベージュ #EAD9B8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ごはん・お買い物系エピソードの小物に</t>
+          <t>フード付きベビーカー。カゴに買い物袋。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>大きな車輪・フードの下で寝顔の赤ちゃん・押す親の汗しずく。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>走行=ガタガタ揺れ / 段差=すっとぶ / 停止=ブレーキのカチャン</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ED08</t>
+          <t>CC08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>特産</t>
+          <t>うちの犬&amp;猫</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>江戸川佃煮</t>
+          <t>ペットはキョトン顔で現場に居合わせる、動く小物（おじゃまキャラ・癒し枠）。ペットが出るエピソードや、おじゃまキャラが必要なときに使う。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>葛西などに老舗佃煮屋が並ぶ町。瓶詰め佃煮が名物。</t>
+          <t>丸い体とふさふさのしっぽ。首輪と鈴。困った人のそばに正座して首をかしげる。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>瓶詰め佃煮の棚や佃煮屋の看板。</t>
+          <t>犬 茶 #B5854B（レトリバー風） / 猫 白 #FFFFFF / 首輪 赤 #E8112D / 鈴 金 #FFD23F</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>お買い物・スーパー系エピソードに</t>
+          <t>首輪と鈴。犬は口に新聞紙か小物。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>犬=たれ耳・はっぱ口 / 猫=三角耳・ひげ・しっぽ。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>待機=しっぽふりふり / 移動=ダッシュ / 発見=首かしげ / おじゃま=前を横切る</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ED09</t>
+          <t>CC09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>じいじ&amp;ばあば</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>都営新宿線</t>
+          <t>わざと遅れて「ちょうどいい」タイミングで駆けつける、頼れる（そして時々穴な）助っ人コンビ。孫の要求には絶対勝てない。祖父母が出るエピソードのとき最有力。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>船堀・一之江・瑞江・篠崎を走る都営新宿線。</t>
+          <t>白髪に丸メガネのじいじ、結んだ髪のばあば。3.5頭身で腰がまがっているが、走ると意外と速い。孫を見つけるとまゆ毛が八の字の満面笑顔。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>青い電車の側面、駅名看板（船堀/一之江/瑞江/篠崎）。</t>
+          <t>肌 #FFE0BE / 髪 白 #E8E8E8 / じいじ ジャケット 紺 #2B3A67 / ばあば 服 花柄ピンク #FFB6C1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>お出かけ・送迎・ダッシュ系エピソードの背景に</t>
+          <t>じいじ=丸メガネ＋紺ジャケット / ばあば=お団子髪＋花柄エプロン。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>じいじ=白髪・丸メガネ・口ひげ / ばあば=お団子・細い眉。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>待機=腰をさすり / 移動=意外と速い小走り / 孫発見=まゆ毛八の字の満面笑顔 / 失敗=こけそうでこけない</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ED10</t>
+          <t>CC10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>三輪車</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JR京葉線・総武線</t>
+          <t>こぎ始めの研究者（笑）、スピードは出ないが情熱は1番。小さな子の移動・追跡系エピソードのとき最有力。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>葛西駅（京葉線）、新小岩・小岩・平井駅（総武線）。</t>
+          <t>サドルの高い三輪車、バックミラー付き。前輪がフラフラして自分の意志で曲がらない。がんばってこぐ子の足が回転より速い。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>駅名看板と通過する電車。</t>
+          <t>フレーム 赤 #E8112D / サドル 黒 #1C1C1C / ハンドルグリップ 白 #FFFFFF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>通勤・お出かけの背景に</t>
+          <t>サドル高め・バックミラー付き・ペダルにスニーカー。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>フラフラな前輪・ミラーに親の顔（小さく）・回るペダル。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>走行=がんばってこぐ足 / 曲線=自分の意志で曲がらない / 停止=フラフラ倒れる</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ED11</t>
+          <t>CC11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>街並み</t>
+          <t>ハムスター</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>住宅街と商店街</t>
+          <t>ほっぺに全部を詰め込む、小さな逃走名手。すきまから脱走して進む。ペット・脱走・回収系エピソードや、おじゃまキャラとして使う。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>低層の戸建て住宅街、大通り沿いの商店街、自転車置き場と電柱・電線。</t>
+          <t>まるい体、詰まったほっぺ、小さな足。高速で回すハムスターホイール、寝床に集めた秘密の貯蔵庫。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>戸建て住宅の並び、八百屋・クリーニング店などの小さな看板、電柱と電線。</t>
+          <t>体 金茶 #D9A45B / ほっぺ・腹 白 #FFF6E8 / 目 黒 #1C1C1C</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>日常系エピソードの既定背景に</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ED12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>街並み</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>タワーホール船堀</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>船堀駅前にある区の文化ホール。逆三角形の特徴的な塔。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>遠景に逆三角形の塔をシルエットで。</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>街のランドマークとして遠景に</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ED13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>施設</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>江戸川区メタバース区役所</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>cluster上の仮想区役所。総合案内や相談窓口が現実さながらに再現されている。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>道しるべ・案内所として「メタバース区役所」の看板を登場させる。</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>メタバース会場つながりの演出に</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ED14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>公式キャラ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>エドリバー</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>江戸川区PRキャラクター。区に住むレトリバーで、頭の上に親友のきんぎょがちょこん。</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>応援役・案内役として、背景や案内看板に登場させる。</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>区の公式キャラクターのため使用は区の許可制。許可が取れている場合のみ登場させ、デザインを変更しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ED15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>文字・看板</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>えどがわ表記</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>看板や案内表示に使われる「えどがわ」「江戸川区」の表記。</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>看板に「えどがわ」の文字。道路標識・バス停名に地区名（葛西/小岩/船堀/瑞江/篠崎/一之江）。</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>看板・標識の文字として散りばめる</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ED16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>自然・風景</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>カルガモと花の風景</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>江戸川や旧江戸川の水面でよく見られるカルガモの親子。春は花の名所が色づく。</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>遠景の水面にカルガモの親子、春の背景に花の色を添える。</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>区の公式シンボルと称せず、風景モチーフとして使う</t>
+          <t>ほっぺにひまわりの種。寝床に紙屑の貯蔵庫。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>詰まったほっぺ・小さな手足・短い尾・はなの点。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>待機=ほっぺもぐもぐ / 移動=ホイール疾走 / 成功=ほっぺチャレンジ / 失敗=くるくる回転</t>
         </is>
       </c>
     </row>
@@ -3187,6 +2785,564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>prompt_text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ED01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>自然・風景</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>江戸川河川敷</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>区の名前の由来でもある一級河川・江戸川と広い河川敷。土手を走るサイクリングロード。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>背景に江戸川の河川敷と土手、サイクリングロード。遠景に江戸川の流れと対岸の街並み。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>屋外・散歩・公園系エピソードの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ED02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>自然・風景</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>旧江戸川と水門</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>区を流れる旧江戸川と、至る所にある水門・堰。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>遠景に旧江戸川の水面と水門。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>水辺・河川系の舞台に</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ED03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>名所</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>葛西臨海公園</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>観覧車・水族館・BBQ広場がある区の代表公園。駅前からすぐ。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>背景に大きな観覧車と水族館のガラスドーム。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>おでかけ系エピソードの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ED04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>名所</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>小岩の菖蒲園と新小岩</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>小岩エリアの菖蒲園、新小岩駅前の商業地。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>春なら菖蒲の花畑、街の賑わいなら新小岩駅前の看板群。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>季節・街の賑わい演出に</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ED05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>名所</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>篠崎公園と区民まつり</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>広大な篠崎公園。秋の区民まつりはテントと屋台が並ぶ。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>テントと屋台が並ぶ公園の広場、幅広の広場と並木。</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>イベント・お祭り系エピソードに</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ED06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>風物詩</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>江戸川花火大会</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>毎年夏、江戸川河川敷で開催される都内最大級の花火大会。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>夜空に大きく開く花火（画面上部の演出としても使える）。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>夜・夏・お祭りの演出に</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ED07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>特産</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>小松菜</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>江戸川区特産の小松菜。名産品・郷土料理の主役。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>小松菜の束や小松菜商品を小物として登場させる。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ごはん・お買い物系エピソードの小物に</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ED08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>特産</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>江戸川佃煮</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>葛西などに老舗佃煮屋が並ぶ町。瓶詰め佃煮が名物。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>瓶詰め佃煮の棚や佃煮屋の看板。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>お買い物・スーパー系エピソードに</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ED09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>都営新宿線</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>船堀・一之江・瑞江・篠崎を走る都営新宿線。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>青い電車の側面、駅名看板（船堀/一之江/瑞江/篠崎）。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>お出かけ・送迎・ダッシュ系エピソードの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ED10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JR京葉線・総武線</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>葛西駅（京葉線）、新小岩・小岩・平井駅（総武線）。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>駅名看板と通過する電車。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>通勤・お出かけの背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ED11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>街並み</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>住宅街と商店街</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>低層の戸建て住宅街、大通り沿いの商店街、自転車置き場と電柱・電線。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>戸建て住宅の並び、八百屋・クリーニング店などの小さな看板、電柱と電線。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>日常系エピソードの既定背景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ED12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>街並み</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>タワーホール船堀</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>船堀駅前にある区の文化ホール。逆三角形の特徴的な塔。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>遠景に逆三角形の塔をシルエットで。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>街のランドマークとして遠景に</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ED13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>施設</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>江戸川区メタバース区役所</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cluster上の仮想区役所。総合案内や相談窓口が現実さながらに再現されている。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>道しるべ・案内所として「メタバース区役所」の看板を登場させる。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>メタバース会場つながりの演出に</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ED14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>公式キャラ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>エドリバー</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>江戸川区PRキャラクター。区に住むレトリバーで、頭の上に親友のきんぎょがちょこん。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>応援役・案内役として、背景や案内看板に登場させる。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>区の公式キャラクターのため使用は区の許可制。許可が取れている場合のみ登場させ、デザインを変更しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ED15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>文字・看板</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>えどがわ表記</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>看板や案内表示に使われる「えどがわ」「江戸川区」の表記。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>看板に「えどがわ」の文字。道路標識・バス停名に地区名（葛西/小岩/船堀/瑞江/篠崎/一之江）。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>看板・標識の文字として散りばめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ED16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>自然・風景</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>カルガモと花の風景</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>江戸川や旧江戸川の水面でよく見られるカルガモの親子。春は花の名所が色づく。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>遠景の水面にカルガモの親子、春の背景に花の色を添える。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>区の公式シンボルと称せず、風景モチーフとして使う</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3321,7 +3477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3337,85 +3493,85 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>story</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>N01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HP01</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>こぼれガード</t>
+          <t>おうちプール開きだ！</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>落ちてくる・こぼれてくる飲み物を、お皿やコップで受け止めて床を守るキャッチ防衛。受け止め損ねた分だけ床の水たまりゲージが増える。</t>
+          <t>トイレットペーパー1ロールを丸ごと流したら便器があふれ出す。ラバーカップで突入したパパに水が跳ねて、廊下に海パン・ゴーグル姿のソウタ「おうちプール、オープンでーす！」</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>N02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HP01</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ふきとりレース</t>
+          <t>おまるはヘルメットだ！</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>床に広がった水たまりを、制限時間内に端からなぞってふき取る。ぬるぬるゾーンに入ると操作が滑り、パックを踏むと再びこぼれる。</t>
+          <t>新品のアヒル型おまるを即座にかぶって「アヒルレンジャー、しゅつどう！」。スーパーのレジで「かっこいい帽子ね」と褒められた瞬間、店中に響く声で「これ、おしっこするとこ！」</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>N03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HP01</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>にげるコップ</t>
+          <t>おむつ替えは0.5秒が命だ！</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>勝手に転がっていくコップ・パックを追いかけて回収する追跡アクション。逃げる物がワープやバウンドして笑わせる。</t>
+          <t>おむつを外して振り向いた瞬間、モモが猛ハイハイで脱走。ヘッドスライディングでキャッチして高々と掲げたら、顔面に第二波。ママは台所から無言。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>N04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3425,19 +3581,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>トイレまでダッシュ</t>
+          <t>うんち実況中継だ！</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>障害物と人混みを左右でよけながら、ゴールのトイレまで走り抜ける。限界ゲージが時間で上昇し、ゲージ満タンでコミカルにゲームオーバー。</t>
+          <t>ファミレスで料理が届いた瞬間にトイレへ。戻るなり大声で「ハンバーグみたいなのとウインナーみたいなの出た！」。ハンバーグを切るママのナイフと隣席のフォークが同時に停止。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>N05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3447,19 +3603,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>道あけ</t>
+          <t>トイレの合言葉はなんだ！</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>前方から流れてくる人・カートをタップで左右に寄せて、通路をこしらえて進む。あける幅とスピードの判断が勝負。</t>
+          <t>出勤前にもれそうなパパ、トイレにはソウタが籠城中。「開けごま！」「ちがいます」。ドアの下から「ヒント：おしりからでるもの」。全開のベランダに向かって絶叫するパパと目が合うお向かいのおじいさん。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>N06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3469,1200 +3625,980 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>背負いバランス</t>
+          <t>おむつがパンになったゾ！</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>背負った対象を落とさないよう左右のバランスを取りながら走る。スピードを出すとふらつき、バランスとスピードのトレードオフ。</t>
+          <t>風呂場が妙に静かだと思ったら、湯船にふくらんだおむつ30枚。在庫ゼロ、夜9時。モモがいきみ始め、パジャマのパパがコンビニへ全力疾走。散歩と勘違いした柴犬も並走。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>N07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HP03</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>あーんリズム</t>
+          <t>渋滞の真犯人だ！</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>口の「あーん!」のタイミングに合わせて食べ物を運ぶリズムアクション。食べられない物が来たら手を引く判断も入る。</t>
+          <t>高速10キロ渋滞で「もれるー！」。しりとりで気をそらし（「レモン水！」「水を言うなー！」）、パーキングにすべり込み間に合った家族のハイタッチ。車に戻ると運転席がしっとり。助手席の犬、目をそらす。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>N08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HP03</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>床まもり</t>
+          <t>謎の臭いの犯人は誰だ！</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>飛び散る食べ物から床をまもる盾操作。ガードできた量より落ちた量が多いとコミカルな「床の食材図鑑」が育つ。</t>
+          <t>リビングが臭い。全員の目が犬へ。濡れ衣で犬小屋でしょんぼりの夜。大捜索の末、パパのカバンから一週間前の納豆巻き発見。「パパがおなかすいたらかわいそうだから！」</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>N09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HP03</t>
+          <t>HP07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>重ねて完成</t>
+          <t>スマホがないないぽちゃんだ！</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>食べられる物を正しい順番に重ねて一品完成させる積みパズル。NG物を積むと全体が崩れて床に直行する。</t>
+          <t>モモが「ないない」とスマホをトイレにぽちゃん。底から着信音、画面には「部長」。手を突っ込むパパの背後から「あ、さっき流すの忘れた」。石化したパパ、なぜか反射的に「はい、もしもし」。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HP04</t>
+          <t>HP13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ねむりゲージ</t>
+          <t>パンツは帽子だ！</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>眠くなるアイテムを順番に使って眠りゲージを満タンにする育成パズル。うるさい音は画面からタップで消しにかかる。</t>
+          <t>冬の朝「ひとりで着替えできた！」。バス停で先生に挨拶し、礼儀正しく帽子を取る園帽の下から恐竜柄のパンツ。足の穴から耳がぴょこん「おみみがあったかいんだよ！」。バスの窓から園児たちの拍手。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HP04</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>音の犯人探し</t>
+          <t>冷蔵庫さんもお風呂だ！</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>寝ている子の周りで鳴る音の発生源を、動きの手がかりから推理して止める静音パズル。外すと目がパッチリ開く。</t>
+          <t>冷蔵庫が全開、中身はぜんぶ床に整列。上半身を突っ込んでゴシゴシ「冷蔵庫さんもお風呂の日！」。モモが卵を1個ずつ「どーぞ」。整列の真ん中でハムをくわえた犬が固まる。目だけがママを見ている。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HP04</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ふとん防衛線</t>
+          <t>いちご全部消えた事件だ！</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>添い寝者の寝返り侵攻から、ふとんの端・子どもの寝場をまもる防衛アクション。侵攻ルートがだんだん読めなくなる。</t>
+          <t>誕生日ケーキを開けたらいちごだけ8粒消失。「犬がたべた！」犬の鼻には生クリーム（塗られた）。パパの胸ポケットからほかほかのいちご8粒。「ポケット、ひんやりしてるから保管した」</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>N13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HP05</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>壁がきミュージアム</t>
+          <t>ママの秘密のチョコがないゾ！</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>壁を這い回る落書きを、スポンジを操作してなぞって消すアクション。消す前に一部「傑作」だけ残す選択ができると得点UP。</t>
+          <t>夜こっそり出したご褒美チョコは妙に軽い。中には紙1枚「ママ ごちそうさまでした」。犯行時刻はパパが「子どもは俺が見てる」と寝落ちしていた30分。「パパの引き出しのおせんべいも、もうないよ」</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>N14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HP05</t>
+          <t>HP14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>名画セーブ</t>
+          <t>ソファでヒヨコをあたためるゾ！</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>流れてくる子どもの「作品」を「保存」と「お片付け」に仕分ける。本物の名作（家族の似顔絵など）を消すとペナルティで周囲が凍りつく。</t>
+          <t>ソファのクッションの下に卵10個「あしたヒヨコが10匹！」。残業帰りのパパがスーツのままドスン。お尻から黄色い汁がポタポタ。「パパがヒヨコつぶしたー！」「まだヒヨコじゃないっ！」</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HP05</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>一筆パズル</t>
+          <t>離乳食スナイパーだ！</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>一筆書きで落書きを完成させ、親が戻ってくる前に壁に「提出」する。提出した絵がリザルトで全員に披露される。</t>
+          <t>「はい、あーん」スプーンをバチーン。かぼちゃが放物線を描いて壁に着弾。パパの大口に見事ストライク、半分は鼻の穴へ。黄色まみれの食卓で「…で、モモは何口食べたの？」答え、ゼロ口。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>N16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HP06</t>
+          <t>HP11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>泡フィーバー</t>
+          <t>男同士の話し合いだ！</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>飛び交う泡を集めてお風呂を完成させる集めアクション。泡だらけの子が脱走するので、時々画面端をタップしてキャッチする。</t>
+          <t>スーパーのお菓子売り場で床に大の字。パパ「任せろ」なぜか隣に寝転んで説得開始。5分後、二人が仲良く手をつないで戻ってくる。カゴにはおまけ付きお菓子3箱とパパのビーフジャーキー。叱られたのはパパ。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>N17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HP06</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>脱走ルート封鎖</t>
+          <t>食パンのおうちだ！</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>泡まみれで脱走しようとする子のルートを読み、障害物と泡を置いてふさぐ。ふさぎすぎると怒りゲージ（笑）が上がる。</t>
+          <t>朝、食パン一斤がぜんぶ「耳だけ」。リビングにパンの耳を積んだ小さなおうち、窓から犬が顔だけ（動くと屋根が崩れる）。「白いところはぼくが食べたから、エコだよ！」</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>N18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HP06</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>湯かげんマスター</t>
+          <t>ファイト課長だ！</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>温度ゲージを調整しながら、目を離さずに入浴を進める管理パズル。熱すぎ・ぬるすぎ・脱走の三すくみを回す。</t>
+          <t>「パパのお弁当のほうが大きい」とこっそり交換。取引先との昼食会議でフタを開けるとクマのキャラ弁。遠足ではのりの文字を読み上げ「ファイト！ かちょう！」。園児全員がのり弁を天に掲げて「かちょー！」</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>N19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HP07</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>スマホガード</t>
+          <t>ふりかけ雪まつりだ！</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>飛びついてくる子の手から、画面を左右操作で守る防衛アクション。守り続けると子が正座でじりじり近づき、距離が縮む。</t>
+          <t>「雪だ！」とふりかけを袋ごと逆さに。弟の頭にのりたまが積雪、大喜びで追加散布。犬は降ってくるたまごの粒を空中キャッチ。止めに入ったパパの顔面にゆかり直撃、眉毛が紫。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HP07</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>取り合いチキンレース</t>
+          <t>納豆ネバネバ大連結だ！</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>じりじり距離を詰めてくる手との距離ゲーム。下ろすタイミングを誤るととられ、早く下ろすと大泣き。判断が勝負。</t>
+          <t>手づかみ納豆を「あげる」と犬の頭へ。糸で赤ちゃんと犬がつながり、逃げるとズルズル。助けに入ったパパのひげにも糸がからまる。「ぼくもつながる！」四者連結完成。ママ「…全員、お風呂」</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>N21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HP08</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>バス追跡ダッシュ</t>
+          <t>ムギがミイラになったゾ！</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>乗り物を左右操作で運転し、信号・坂・障害物を越えて追跡対象に追いつく。追いつくごとに距離ゲージが回復する。</t>
+          <t>ティッシュ5箱が空、床一面が白い海。犬をぐるぐる巻き「ミイラはえいえんに生きられるんだよ」。帰宅したパパ、暗い廊下をヨロヨロ歩く白い四つ足に悲鳴。全力疾走でほどけたティッシュが廊下に10メートル。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>N22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HP08</t>
+          <t>HP05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>信号判断走行</t>
+          <t>せかいいちきれいなママだ！</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>青・赤の瞬時判断で進むか止まるかを決める。赤での突入は減速・回り道になり、判断の積み重ねで差が開く。</t>
+          <t>子ども部屋の壁一面に油性ペンで巨大な家族の絵。怒りかけたママ、気づく。絵のママは王冠つきで「せかいいちきれい」。「…まあ、上手ね」。隣のパパはつるつる頭に鼻毛3本、説明は「ねてるパパ」。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>N23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HP08</t>
+          <t>HP05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>近道パズル</t>
+          <t>うずまき課長だ！</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>分岐する路地から追跡対象に近づける道を選ぶルートパズル。選んだ道ごとにコミカルな障害が待つ。</t>
+          <t>昼寝中のパパの顔に油性ペンでうずまき・巻きヒゲ・額に「ぱぱ」。アラームで飛び起き「やばい、会議！」顔も洗わずカメラON。画面の全員が無言、肩だけ小刻みに震える。部長「内容はいいんだけど、うずまきが気になって入ってこない」</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>N24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HP09</t>
+          <t>HP13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>しーっ!ステルス</t>
+          <t>パンツの柴犬だ！</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>音を立てずに散らかった物を回収するステルス回収。音の出る物の扱いが難しく、音を立てると静寂が破られて大惨事のまま発見される。</t>
+          <t>「洗濯物たたむの、お手伝いする！」洗濯物はぜんぶ犬が着ていた。頭にはパパのパンツ、耳は足の穴から。宅配便のすきに犬が脱走。翌朝お隣さん「パンツ、似合ってましたね」。パパ「俺じゃないです」</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T25</t>
+          <t>N25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HP09</t>
+          <t>HP10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>痕跡パズル</t>
+          <t>その口紅、誰のだ！</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>足跡・痕跡・証拠品をたどって「何が起きたか」を再現する推理パズル。再現するほど真相（の笑い）が明かされる。</t>
+          <t>ママの口紅でおけしょうごっこ。抱っこされた赤ちゃんがパパの白いワイシャツの胸にチュッ。お風呂上がりのママ「…この口紅、誰の？」真っ赤な口の兄が割って入る「パパ、モテモテだね！」</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T26</t>
+          <t>N26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HP09</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>静か計</t>
+          <t>ぜんぶぼくのものだ！</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>「やけに静か」の時間の長さに応じて、事態が何に進化したかを早めに推測して対応する予測パズル。対応が遅れるほど事態が拡大する。</t>
+          <t>おばあちゃんから「ぼくのもの」シール200枚が届く。テレビ、炊飯器、赤ちゃんのおでこ、犬のお尻、便座のフタ。帰宅したパパ、背中に貼られてちょっとジーン。最後の1枚は限定ビールへ「これがいちばん、ぼくのもの」</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T27</t>
+          <t>N27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HP10</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>化粧品ディフェンス</t>
+          <t>粉まみれおばけ屋敷だ！</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>化粧品に飛びつく子の手を、代替品を渡してそらす対応アクション。渡す物を間違えると意図しないコラボメイクが完成する。</t>
+          <t>帰宅したママ、暗い廊下から「うらめしや〜」。真っ白な兄弟、くしゃみする犬、足元に小麦粉の空き袋。「…怖いのは後片付けよ」。背後に真っ白な大人のおばけ「いや、俺もやれって言われて…」ゲホッ。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T28</t>
+          <t>N28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HP10</t>
+          <t>HP06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>肌にOK/NG</t>
+          <t>泡の国の仙人だ！</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>流れてくる化粧品・日用品を「肌にOK」「NG」に仕分ける。NGを通すと画面の顔がコミカルに進化していく。</t>
+          <t>手を洗いに行った息子が戻らない。洗面所がひざまで泡「ばいきんは泡でやっつける！」。泡の中から羊になった犬が立ち上がりブルブルッ。のぞいたパパにシェービングフォーム噴射、白ひげの仙人誕生。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T29</t>
+          <t>N29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HP10</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>鏡のまちがい</t>
+          <t>そうたのいえだ！</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>完成した「作品」のメイクのまちがいを、親の本来の顔を見比べて直す修正パズル。直すほど本人の納得顔が変わる。</t>
+          <t>段ボールのひみつ基地完成「おとなは入っちゃダメ」。パパ「明日出す書類、どこいった…？」基地のカーテンも表札もパパの書類。表札は「そうたのいえ」。取り返そうと頭を突っ込んだパパ、抜けなくなる。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HP11</t>
+          <t>HP09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>視線ゲージ</t>
+          <t>おばあちゃん来訪3分前だ！</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>次々来るおねだりをさばきながら、周囲の視線ゲージを上限以下に保つ管理アクション。最後の手段（代わりの商品・店員の助け）は回数制限あり。</t>
+          <t>姑の初訪問、朝から大掃除で家はピカピカ。玄関で髪を整えて振り返るとリビングが元の惨状。「おばあちゃん、いつものおうちが見たいって言ってた！」義母「あら、思ってたより片付いてるじゃない」。ママの笑顔にピシッとひび。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>N31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HP11</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>視線かくれんぼ</t>
+          <t>パパは重症患者だ！</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>おねだりの対象になりそうな商品を、子の視線が届かない位置に配置し直す隠すパズル。配置が甘いと視線ロックされる。</t>
+          <t>昼寝中のパパに医師・助手・看護師（犬）が「しゅじゅつをはじめます」。全身トイレットペーパー包帯、顔中ばんそうこう、頭にちょんまげ。ママに報告「パパはじゅうしょうです。おさらあらいできません」。包帯の上からエプロンを巻くママ。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>N32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HP11</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>寝そべり対応</t>
+          <t>限定ロボが合体したゾ！</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>床で寝そべった子に対して、どう対応するかのカードを素早く選ぶ判断ゲーム。対応の組み合わせで成否とオチが変わる。</t>
+          <t>パパが半年かけて塗った限定ロボのプラモデル。右腕にウサギのぬいぐるみがガムテープで合体、背中に紙皿の翼「ともだちと合体したから、100ばいつよい！」。取り返そうとした瞬間、赤ちゃんがロボごと抱きしめて昼寝。パパ、正座で待機。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T33</t>
+          <t>N33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HP12</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>迷言カルタ</t>
+          <t>お馬さんがちゃぶ台になったゾ！</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>読み上げ・出題に合う迷言札を取るカルタ風。本物の正しい言葉札と迷言札が並び、どちらを取るかの判断も入る。</t>
+          <t>お馬さんパパの背中に兄と弟、なぜか犬まで乗車。腰から「グキッ」。四つんばいのまま動けない「このままでいさせてくれ」。背中にみかんのカゴ、絵本、犬のおもちゃ、ママの湯のみ。家族のちゃぶ台になる。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T34</t>
+          <t>N34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HP12</t>
+          <t>HP18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>正しい読みは?</t>
+          <t>パパが散歩されるゾ！</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>流れてくる言葉を「正解読み」「うちの迷言」に仕分ける。迷言と判定するほど家族の迷言帳が増えていく。</t>
+          <t>寝ぼけたパジャマパパの散歩で猫を見つけた犬がロケットスタート、サンダルが片方飛ぶ。公園のラジオ体操の列のど真ん中を柴犬とパジャマ男が駆け抜ける。植え込みにダイブしたパパに「パパ、いちばん！」参加者から拍手。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T35</t>
+          <t>N35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HP12</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>発音ペア合わせ</t>
+          <t>おならの犯人はムギじゃないゾ！</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>発音（オノマトペ・読み上げ）と文字のペアを合わせる神経衰弱。正解のペアと迷言のペアが混ざる。</t>
+          <t>お正月、おじいちゃんの挨拶中に「プゥ〜〜」。「こら、犬！」犬は耳を伏せてこたつへ。「パパ、おならは犬のせいにすればいいっていつも言ってたもんね！」親戚全員がパパを見る。こたつから顔だけ出した犬もパパを見る。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T36</t>
+          <t>N36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HP13</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>コーデ条件パズル</t>
+          <t>まくら投げで全員正座だ！</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>「これがいい!」という子のこだわり条件を満たす服の組み合わせを作る条件パズル。条件が増えるほど組み合わせが難しくなる。</t>
+          <t>寝る前、枕がパパの顔に命中「…やったな」。大人げない全面戦争、パパの剛速球は犬が空中キャッチ。「とどめだー！」は照明に直撃、ガシャーン真っ暗。ドアの前にママのシルエット「兄3分、弟1分、犬許す、パパ30分」</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T37</t>
+          <t>N37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HP13</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>服却下バランス</t>
+          <t>恐竜パパが届いたゾ！</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>出てくる服を「OK」「却下」に仕分ける。却下しすぎると大泣きゲージが上がり、着せ直しのタイムロスになる。</t>
+          <t>身に覚えのない荷物、中身は大人用ティラノサウルスの着ぐるみ。「ボタン押したら、恐竜がくるって言ってた！」仕方なく着たパパ、だんだん本気になり「ガオーッ！」と玄関まで追走。ドアの向こうの宅配便さん「…ハンコお願いします」</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T38</t>
+          <t>N38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HP13</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>着替え補助タップ</t>
+          <t>ソウタが犬になったゾ！</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>自分で着ようとする子の、詰まる瞬間（ボタン・袖）だけをタイミングよく補助するタップゲーム。補助しすぎると「じぶんで!」でリセット。</t>
+          <t>「きょうから犬のおうちで暮らす」犬小屋に籠城、追い出された犬は家の中へ。朝、寝室ではパパが犬に腕枕してスヤスヤ。犬小屋に「起きなさい」と声をかけると、中から元気に「ワン！」</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T39</t>
+          <t>N39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HP14</t>
+          <t>HP16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>セーフキャッチ</t>
+          <t>サプライズは全部バレてるゾ！</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>危険物に伸びてくる手を間一髪で止める反応アクション。安全な物・困ったことになりそうな物の区別も入る。</t>
+          <t>パパの誕生日、玄関で「ケーキないよ！ 冷蔵庫にはないからね！」。パパ、演技で「そうか、ないのかー」。暗闇でクラッカー、驚いた犬がケーキに顔からダイブ。顔を上げた犬の頭に「おたんじょうび おめでとう パパ」のプレート。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T40</t>
+          <t>N40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HP14</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>危険か安全か</t>
+          <t>中まで洗車だ！</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>出てくる物・行動を一瞬で「安全」「危険」に振り分ける瞬時判定。判定を学べる1行メモが結果画面に表示される。</t>
+          <t>洗剤を取った2分間、息子にホースを預けた。戻ると後部座席のドアが全開「中もきれいにしないと！」。車内の床に水たまり、フロアマットがぷかぷか、びしょぬれの犬が着席。「エンジンのとこも洗ってあげたよ！」ボンネットが少し開いている。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T41</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HP14</t>
+          <t>HP18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>立ち入り封鎖</t>
+          <t>モモが消えたゾ！</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>危険ゾーンへの子の侵攻ルートを、安全グッズでふさぐ配置パズル。ふさぎ方で子の迂回ルートが変わる。</t>
+          <t>振り返ると赤ちゃんがいない。兄も「モモー！」と叫びながら冷蔵庫を開けて確認。パパが通報しかけた時、兄が犬用ベッドを指さす。犬のおなかの毛から足が2本、耳をくわえて爆睡、犬は目で「早くなんとかして」</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T42</t>
+          <t>N42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HP15</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>寝相防衛</t>
+          <t>パパの髪、一本どーぞだ！</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>大寝返りの侵攻から、まもるべき子・空间を守る防衛アクション。侵攻パターンが増えていく。</t>
+          <t>赤ちゃんがパパの貴重な前髪をがっちりロック。袖をくわえた犬との綱引きの末、プチッ。満面の笑みで1本差し出す「ぱぱ、どーぞ」。パパ、涙ぐんで財布にしまう。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T43</t>
+          <t>N43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HP15</t>
+          <t>HP18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>寝言しらべ</t>
+          <t>キラキラ泥棒の隠れ家だ！</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>集めた寝言の断片を組み合わせて一文にするお題合わせ。完成文がリザルトで発表される。</t>
+          <t>車の鍵、ピアス、リモコン、スプーンが次々消える。容疑者は犬。犬小屋をのぞくと盗品の山の上に、ネックレス三重巻きの赤ちゃんが鎮座「きらきら」。自分の家に入れない犬、外で雨に濡れている。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T44</t>
+          <t>N44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HP15</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ふとん返送</t>
+          <t>盆栽からピーマンが出たゾ！</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>端から落ちかけた対象をふとんの中央へ戻すバランス操作。戻しすぎるとまた逆側に転がる往圧ジレンマ。</t>
+          <t>パパ自慢の盆栽が、なんだか酸っぱいにおい。根元を掘るとピーマン、にんじん、しいたけが地層になって出土。夕食のピーマンを前に、そっと席を立つ息子「やさいは土にかえすと、また生えてくるんだよ」</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>T45</t>
+          <t>N45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HP16</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>お菓子配給</t>
+          <t>目をつぶれば透明人間だ！</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>機嫌ゲージを保ちながら、お菓子を配って場を収める配給アクション。配りすぎるとママ怒りゲージ（遠くのシルエット）が上昇する。</t>
+          <t>目をぎゅっとつぶったまま冷蔵庫のプリンを食べる息子。両親、乗っかる「あれー？ ソウタどこー？」パパ「透明人間がいたらここに座ってたりして」ソウタの上にドスン。「見えてないのに、なんでぼくの上に座るの！」手には2個目のプリン。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>T46</t>
+          <t>N46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HP16</t>
+          <t>HP12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ばれる前に</t>
+          <t>はじめての言葉は生中継だ！</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>証拠（お菓子の袋・散らかり）を、ママの足音が近づく前に片付けるステルス片付け。片付けの順番と音の判断が勝負。</t>
+          <t>祖父母とビデオ通話「ばーばって言ってごらん」。パパは「ぱ・ぱ」、ママは「ま・ま」と口パクで必死アピール。赤ちゃん、画面をまっすぐ見て「うんち」。兄「やったー！ ぼくが毎日教えたやつ！」おじいちゃんはお茶を噴く。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T47</t>
+          <t>N47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HP17</t>
+          <t>HP12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>砦防衛</t>
+          <t>パパのおしごと発表会だ！</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>迫ってくる要求・侵攻から、作品やお気に入りをまもる防衛アクション。まもる位置取りと要求のさばき方が勝負。</t>
+          <t>参観日、テーマは「おうちの人のおしごと」。パパ、誇らしげに背筋を伸ばす。口を開けて寝るパパの絵を掲げ「パパのおしごとは、かいぎで寝ることです！ ママが言ってました！」パパが横を見ると、ママは窓の外の空を見つめていた。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>T48</t>
+          <t>N48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HP17</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>分け前調停</t>
+          <t>怪獣モモが街をこわすゾ！</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>取り合いになっている物を、どう分けるかの配分カードでさばく判断ゲーム。納得の配分で笑いが起きる。</t>
+          <t>3日かけて作ったブロックの街に、怪獣の赤ちゃんが接近。「防衛隊しゅつどう！」パパ、立ちはだかる。モモがニコッ「…かわいい」自ら街の上に倒れて全壊。パパの上で「がおー！」兄「パパ、うらぎりものー！」</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>T49</t>
+          <t>N49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HP18</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.5秒追跡</t>
+          <t>サンタさんへの手紙は冷凍庫だ！</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>見えなくなった対象を、足跡・視線・鳴き声などの手がかりを頼りに追う追跡アクション。手がかりは時々ハズれも出る。</t>
+          <t>「サンタさんは北極にいるから、冷たいところに入れれば届く」。深夜、アイスを取ろうとしたパパが冷凍庫で手紙を発見。横には凍った犬の骨ガムとパパの靴下「おみやげです」。手紙「パパのおならがくさくなくなりますように」</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>T50</t>
+          <t>N50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HP18</t>
+          <t>HP00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>目撃推理</t>
+          <t>最高の家族写真だ！</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>増えていく目撃情報を組み合わせて、対象の居場所を推理する推理パズル。推理が当たると無邪気な発見シーンに繋がる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>T51</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>HP19</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>みまもり限定</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>「じぶんでやる!」の最中に手を出さずに見守る我慢ゲージ管理。手を出すと減点、詰まった瞬間だけ我慢ゲージを消費して補助できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>T52</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>HP19</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>詰まった瞬間補助</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>自分で進める子の詰まる瞬間だけタイミングよく補助するタップゲーム。補助なしで通すと時間がかかるが得点UP。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>T53</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>HP00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>あるあるカルタ</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>エピソードに登場する物・場面が札になって流れてくる。お題に合う札を素早く取るカルタ取り。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>T54</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>HP00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>事件再現</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>散らかった・こぼれた事態を、順番を考えて元に戻す片付けパズル。戻す手順でオチが変わる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>T55</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>HP00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>どっちの対応?</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>進行する事態に対して2択対応を重ねて切り抜ける判断ゲーム。選択の積み重ねで結末が変わる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>T56</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>HP07</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>スワイプまもり</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>飛びついてくる手をスワイプでかわしながら、まもりたい物を守る回避アクション。かわし損ねると距離が一気に縮まる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>T57</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>HP16</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>シルエット監視</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>遠くで近づいてくる「雷」のシルエットの距離と、場を収めるペースのバランスを取る管理アクション。収めるほどシルエットが遠のく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>T58</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>HP17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>要求さばき</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>左右から飛び込んでくる要求を、1人で振り分けてさばく対応アクション。さばき遅れで要求ゲージが溜まると大事件に発展する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>T59</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>HP18</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>方向推理レース</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>一瞬だけ見えた手がかりから進む方向を選び、消えた対象を追いかける連続判断アクション。判断の積み重ねで追いつく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>T60</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>HP19</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>こだわり達成サポート</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>子が自分で進める物事の手順から、触らずに見守りつつ危ない物だけ除去する監視アクション。除去のタイミング判断が勝負。</t>
+          <t>写真館で家族写真「はい、こっち見てくださーい」。赤ちゃんおむつ脱走、犬が追って背景布に突入、兄は白目の変顔。身を乗り出したパパが背景ごと倒れ、ママ絶叫、パシャッ。その一枚が、今もリビングの一番目立つ場所に飾られている。</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4688,216 +4624,1337 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>hp_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>desc</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>core</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GM01</t>
+          <t>T01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>星集め</t>
+          <t>HP01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>コース中に隠れた星・ボーナスアイテムを集める。集めるとリザルト画面が豪華になる（花火・レインボー）</t>
+          <t>こぼれガード</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>落ちてくる・こぼれてくる飲み物を、お皿やコップで受け止めて床を守るキャッチ防衛。受け止め損ねた分だけ床の水たまりゲージが増える。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GM02</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>コンボタイム</t>
+          <t>HP01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>一定コンボを達成すると短いボーナスタイムが発動（出現ペースが上がり得点2倍）</t>
+          <t>ふきとりレース</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>床に広がった水たまりを、制限時間内に端からなぞってふき取る。ぬるぬるゾーンに入ると操作が滑り、パックを踏むと再びこぼれる。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GM03</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>フィーバー</t>
+          <t>HP01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>お助けアイテム取得で一時フィーバー。画面がカラフルになり、すべてがプラス判定になる</t>
+          <t>にげるコップ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>勝手に転がっていくコップ・パックを追いかけて回収する追跡アクション。逃げる物がワープやバウンドして笑わせる。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GM04</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>おじゃま中断</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ときどきおじゃま要素（飼い犬・ロボ掃除機・泡・風 など）が画面を横切って邪魔をする</t>
+          <t>トイレまでダッシュ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>障害物と人混みを左右でよけながら、ゴールのトイレまで走り抜ける。限界ゲージが時間で上昇し、ゲージ満タンでコミカルにゲームオーバー。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GM05</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>難易度カーブ</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>最初は広い判定・ゆっくり、後半はシビア・高速になる難易度カーブ</t>
+          <t>道あけ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>前方から流れてくる人・カートをタップで左右に寄せて、通路をこしらえて進む。あける幅とスピードの判断が勝負。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GM06</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>リワインド</t>
+          <t>HP02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>最後のミスで1回だけ直前の5秒に戻れる</t>
+          <t>背負いバランス</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>背負った対象を落とさないよう左右のバランスを取りながら走る。スピードを出すとふらつき、バランスとスピードのトレードオフ。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GM07</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>分岐イベント</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>途中で2択イベントが挟まり、選択によって場面展開が変わる</t>
+          <t>あーんリズム</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>口の「あーん!」のタイミングに合わせて食べ物を運ぶリズムアクション。食べられない物が来たら手を引く判断も入る。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GM08</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>大物ゲスト</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>途中で大物（祖父母・ペット・園長先生・宅配業者 など）が登場し、場面が一回変わる</t>
+          <t>床まもり</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>飛び散る食べ物から床をまもる盾操作。ガードできた量より落ちた量が多いとコミカルな「床の食材図鑑」が育つ。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GM09</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>隠しオチ</t>
+          <t>HP03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>条件を満たすとリザルトのあとに隠しオチ（子どものもう一言）が出る</t>
+          <t>重ねて完成</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>食べられる物を正しい順番に重ねて一品完成させる積みパズル。NG物を積むと全体が崩れて床に直行する。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GM10</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>逆操作ステージ</t>
+          <t>HP04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>最後の10秒だけ左右操作が反転する（子ども目線ステージ）</t>
+          <t>ねむりゲージ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>眠くなるアイテムを順番に使って眠りゲージを満タンにする育成パズル。うるさい音は画面からタップで消しにかかる。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GM11</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>連打チャージ</t>
+          <t>HP04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>連打でゲージを溜めて、必殺技（一気に回収・スーパーダッシュ など）を発動できる</t>
+          <t>音の犯人探し</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>寝ている子の周りで鳴る音の発生源を、動きの手がかりから推理して止める静音パズル。外すと目がパッチリ開く。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GM12</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ズームのぞき</t>
+          <t>HP04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>画面の一部を長押しでズームして見られる（まちがい探し・痕跡捜索系と相性が良い）</t>
+          <t>ふとん防衛線</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>添い寝者の寝返り侵攻から、ふとんの端・子どもの寝場をまもる防衛アクション。侵攻ルートがだんだん読めなくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HP05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>壁がきミュージアム</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>壁を這い回る落書きを、スポンジを操作してなぞって消すアクション。消す前に一部「傑作」だけ残す選択ができると得点UP。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HP05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>名画セーブ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>流れてくる子どもの「作品」を「保存」と「お片付け」に仕分ける。本物の名作（家族の似顔絵など）を消すとペナルティで周囲が凍りつく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HP05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>一筆パズル</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>一筆書きで落書きを完成させ、親が戻ってくる前に壁に「提出」する。提出した絵がリザルトで全員に披露される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HP06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>泡フィーバー</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>飛び交う泡を集めてお風呂を完成させる集めアクション。泡だらけの子が脱走するので、時々画面端をタップしてキャッチする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HP06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>脱走ルート封鎖</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>泡まみれで脱走しようとする子のルートを読み、障害物と泡を置いてふさぐ。ふさぎすぎると怒りゲージ（笑）が上がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HP06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>湯かげんマスター</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>温度ゲージを調整しながら、目を離さずに入浴を進める管理パズル。熱すぎ・ぬるすぎ・脱走の三すくみを回す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HP07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>スマホガード</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>飛びついてくる子の手から、画面を左右操作で守る防衛アクション。守り続けると子が正座でじりじり近づき、距離が縮む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HP07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>取り合いチキンレース</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>じりじり距離を詰めてくる手との距離ゲーム。下ろすタイミングを誤るととられ、早く下ろすと大泣き。判断が勝負。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HP08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>バス追跡ダッシュ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>乗り物を左右操作で運転し、信号・坂・障害物を越えて追跡対象に追いつく。追いつくごとに距離ゲージが回復する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HP08</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>信号判断走行</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>青・赤の瞬時判断で進むか止まるかを決める。赤での突入は減速・回り道になり、判断の積み重ねで差が開く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HP08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>近道パズル</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>分岐する路地から追跡対象に近づける道を選ぶルートパズル。選んだ道ごとにコミカルな障害が待つ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HP09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>しーっ!ステルス</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>音を立てずに散らかった物を回収するステルス回収。音の出る物の扱いが難しく、音を立てると静寂が破られて大惨事のまま発見される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HP09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>痕跡パズル</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>足跡・痕跡・証拠品をたどって「何が起きたか」を再現する推理パズル。再現するほど真相（の笑い）が明かされる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HP09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>静か計</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>「やけに静か」の時間の長さに応じて、事態が何に進化したかを早めに推測して対応する予測パズル。対応が遅れるほど事態が拡大する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HP10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>化粧品ディフェンス</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>化粧品に飛びつく子の手を、代替品を渡してそらす対応アクション。渡す物を間違えると意図しないコラボメイクが完成する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HP10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>肌にOK/NG</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>流れてくる化粧品・日用品を「肌にOK」「NG」に仕分ける。NGを通すと画面の顔がコミカルに進化していく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HP10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>鏡のまちがい</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>完成した「作品」のメイクのまちがいを、親の本来の顔を見比べて直す修正パズル。直すほど本人の納得顔が変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HP11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>視線ゲージ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>次々来るおねだりをさばきながら、周囲の視線ゲージを上限以下に保つ管理アクション。最後の手段（代わりの商品・店員の助け）は回数制限あり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HP11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>視線かくれんぼ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>おねだりの対象になりそうな商品を、子の視線が届かない位置に配置し直す隠すパズル。配置が甘いと視線ロックされる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HP11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>寝そべり対応</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>床で寝そべった子に対して、どう対応するかのカードを素早く選ぶ判断ゲーム。対応の組み合わせで成否とオチが変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HP12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>迷言カルタ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>読み上げ・出題に合う迷言札を取るカルタ風。本物の正しい言葉札と迷言札が並び、どちらを取るかの判断も入る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HP12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>正しい読みは?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>流れてくる言葉を「正解読み」「うちの迷言」に仕分ける。迷言と判定するほど家族の迷言帳が増えていく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HP12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>発音ペア合わせ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>発音（オノマトペ・読み上げ）と文字のペアを合わせる神経衰弱。正解のペアと迷言のペアが混ざる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HP13</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>コーデ条件パズル</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>「これがいい!」という子のこだわり条件を満たす服の組み合わせを作る条件パズル。条件が増えるほど組み合わせが難しくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HP13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>服却下バランス</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>出てくる服を「OK」「却下」に仕分ける。却下しすぎると大泣きゲージが上がり、着せ直しのタイムロスになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HP13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>着替え補助タップ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>自分で着ようとする子の、詰まる瞬間（ボタン・袖）だけをタイミングよく補助するタップゲーム。補助しすぎると「じぶんで!」でリセット。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HP14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>セーフキャッチ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>危険物に伸びてくる手を間一髪で止める反応アクション。安全な物・困ったことになりそうな物の区別も入る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HP14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>危険か安全か</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>出てくる物・行動を一瞬で「安全」「危険」に振り分ける瞬時判定。判定を学べる1行メモが結果画面に表示される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HP14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>立ち入り封鎖</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>危険ゾーンへの子の侵攻ルートを、安全グッズでふさぐ配置パズル。ふさぎ方で子の迂回ルートが変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HP15</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>寝相防衛</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>大寝返りの侵攻から、まもるべき子・空间を守る防衛アクション。侵攻パターンが増えていく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HP15</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>寝言しらべ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>集めた寝言の断片を組み合わせて一文にするお題合わせ。完成文がリザルトで発表される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HP15</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ふとん返送</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>端から落ちかけた対象をふとんの中央へ戻すバランス操作。戻しすぎるとまた逆側に転がる往圧ジレンマ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HP16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>お菓子配給</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>機嫌ゲージを保ちながら、お菓子を配って場を収める配給アクション。配りすぎるとママ怒りゲージ（遠くのシルエット）が上昇する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HP16</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ばれる前に</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>証拠（お菓子の袋・散らかり）を、ママの足音が近づく前に片付けるステルス片付け。片付けの順番と音の判断が勝負。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HP17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>砦防衛</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>迫ってくる要求・侵攻から、作品やお気に入りをまもる防衛アクション。まもる位置取りと要求のさばき方が勝負。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HP17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>分け前調停</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>取り合いになっている物を、どう分けるかの配分カードでさばく判断ゲーム。納得の配分で笑いが起きる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HP18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.5秒追跡</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>見えなくなった対象を、足跡・視線・鳴き声などの手がかりを頼りに追う追跡アクション。手がかりは時々ハズれも出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HP18</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>目撃推理</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>増えていく目撃情報を組み合わせて、対象の居場所を推理する推理パズル。推理が当たると無邪気な発見シーンに繋がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HP19</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>みまもり限定</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>「じぶんでやる!」の最中に手を出さずに見守る我慢ゲージ管理。手を出すと減点、詰まった瞬間だけ我慢ゲージを消費して補助できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HP19</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>詰まった瞬間補助</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>自分で進める子の詰まる瞬間だけタイミングよく補助するタップゲーム。補助なしで通すと時間がかかるが得点UP。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HP00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>あるあるカルタ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>エピソードに登場する物・場面が札になって流れてくる。お題に合う札を素早く取るカルタ取り。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HP00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>事件再現</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>散らかった・こぼれた事態を、順番を考えて元に戻す片付けパズル。戻す手順でオチが変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HP00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>どっちの対応?</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>進行する事態に対して2択対応を重ねて切り抜ける判断ゲーム。選択の積み重ねで結末が変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HP07</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>スワイプまもり</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>飛びついてくる手をスワイプでかわしながら、まもりたい物を守る回避アクション。かわし損ねると距離が一気に縮まる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HP16</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>シルエット監視</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>遠くで近づいてくる「雷」のシルエットの距離と、場を収めるペースのバランスを取る管理アクション。収めるほどシルエットが遠のく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HP17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>要求さばき</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>左右から飛び込んでくる要求を、1人で振り分けてさばく対応アクション。さばき遅れで要求ゲージが溜まると大事件に発展する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HP18</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>方向推理レース</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>一瞬だけ見えた手がかりから進む方向を選び、消えた対象を追いかける連続判断アクション。判断の積み重ねで追いつく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HP19</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>こだわり達成サポート</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>子が自分で進める物事の手順から、触らずに見守りつつ危ない物だけ除去する監視アクション。除去のタイミング判断が勝負。</t>
         </is>
       </c>
     </row>
@@ -4912,7 +5969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4928,364 +5985,211 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>game_text</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>illust_text</t>
+          <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CD01</t>
+          <t>GM01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>得意顔エンド</t>
+          <t>星集め</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>子どもは一切悪気なし。ゲーム内でも最後に子どもが自慢げにドヤ顔ポーズをとり、親も呆れつつ笑って受け入れる演出を入れる。失敗時も罰ではなく「大変なことになった!」のコミカル演出。</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>子どもは無邪気で満面のドヤ顔。親は驚きつつも笑顔。子どもが「悪者」に見えない構図。</t>
+          <t>コース中に隠れた星・ボーナスアイテムを集める。集めるとリザルト画面が豪華になる（花火・レインボー）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CD02</t>
+          <t>GM02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>純粋すぎる一発オチ</t>
+          <t>コンボタイム</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>エピソードのオチ（子どもの無邪気な一言・行動）をリザルト画面で大写しにする。子どもの核心を突く一言が一番の見せ場。</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>子どもの無邪気な一言（フキダシ）を1コマのオチとして大きく配置。親の反応が顔芸で伝わる構図。</t>
+          <t>一定コンボを達成すると短いボーナスタイムが発動（出現ペースが上がり得点2倍）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CD03</t>
+          <t>GM03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>破壊力スローモーション</t>
+          <t>フィーバー</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ハプニングが起こる瞬間（こぼれる・散らかる・脱走開始）を一瞬のスローモーション+ズームで大げさに演出する。ヒットストップと画面シェイクで「事件感」を笑いに変える。</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ハプニング発生の瞬間をスローモーション風に切り取る。飛び散るものの軌跡と動きの線で「事件の迫力」を笑いに。</t>
+          <t>お助けアイテム取得で一時フィーバー。画面がカラフルになり、すべてがプラス判定になる</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CD04</t>
+          <t>GM04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>親の顔芸リアクション</t>
+          <t>おじゃま中断</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>親の顔がコミカルに変化する（固まる・のけぞる・回転する・青ざめる）。操作キャラの親の反応芸が画面ジュースの主役。</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>親の大げさな表情（顔芸）を1コマの見どころに。子どもの無邪気さとのギャップで笑う構図。</t>
+          <t>ときどきおじゃま要素（飼い犬・ロボ掃除機・泡・風 など）が画面を横切って邪魔をする</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CD05</t>
+          <t>GM05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>勝手に進む子ども</t>
+          <t>難易度カーブ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>操作とは関係なく子ども（またはハプニング源）が勝手に動き出す演出。プレイヤー＝親は「追いつく・止める・回収する」側で、子どもの自由さがゲームの推進力になる。</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>自分の世界に入って自由に動く子どもと、それを追いかける親。子どもが主導権を持つ構図。</t>
+          <t>最初は広い判定・ゆっくり、後半はシビア・高速になる難易度カーブ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CD06</t>
+          <t>GM06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>コミカル物理</t>
+          <t>リワインド</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>バウンドする・ヌルヌル滑る・フワフワ浮く・くるくる回るなど、誇張された物理挙動でハプニングの「無茶」を笑えるものにする。現実の危険さは表現しない。</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>物理法則を無視したコミカルな動き（浮く・滑る・回る）を静止画でもわかるように。誇張された動きの線。</t>
+          <t>最後のミスで1回だけ直前の5秒に戻れる</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CD07</t>
+          <t>GM07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>証拠隠滅パロディ</t>
+          <t>分岐イベント</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>子どもが無邪気に「証拠」を隠そうとする（笑）パロディ演出。捜索パートやリプレイで犯人の無邪気な行動をムービー風に振り返る。</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>「犯人」っぽく構える子どもと、何も知らない純粋な表情のギャップ。</t>
+          <t>途中で2択イベントが挟まり、選択によって場面展開が変わる</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CD08</t>
+          <t>GM08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>なぜなに純粋顔</t>
+          <t>大物ゲスト</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>子どもは「なんで怒られるの?」という純粋な疑問顔。親のツッコミ（フキダシ）と子どもの純粋顔の掛け合いが笑いの軸。</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>真顔で純粋な疑問を投げる子どもと、説明を諦めた親。フキダシの掛け合いで笑う構図。</t>
+          <t>途中で大物（祖父母・ペット・園長先生・宅配業者 など）が登場し、場面が一回変わる</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CD09</t>
+          <t>GM09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ご褒美のハグ</t>
+          <t>隠しオチ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>失敗・成功どちらのエンドでも、最後は親子で笑い合う/ハグする演出で締める。子育ての大変さを「愛おしさ」で受け止める余韻。</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>事件の後でも親子が仲良く笑い合う余韻のある構図。</t>
+          <t>条件を満たすとリザルトのあとに隠しオチ（子どものもう一言）が出る</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CD10</t>
+          <t>GM10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>無邪気顔ウォッチ</t>
+          <t>逆操作ステージ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>子どもの無邪気な顔を画面の片隅（または場面内）に大きく常時表示し、状況で表情が変わる。コンボ中=にっこり、ミス=「え?」ときょとん、ピンチ=わくわく照れ顔、リザルト=ドヤ顔。親だけが必死で、子どもは無邪気——この対比が笑いの軸。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>子どもの無邪気で満面な笑顔（またはきょとん顔）を1コマの中心に大きく。親の必死な顔との対比で笑いを生む。</t>
+          <t>最後の10秒だけ左右操作が反転する（子ども目線ステージ）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CD11</t>
+          <t>GM11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>親のツッコミ漫才</t>
+          <t>連打チャージ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>親のフキダシツッコミ（「まって」「なんで!?」「きょうは寒いからね…」）が笑いのアクセントになる漫才スタイル。子どもの行動と親のツッコミの掛け合いで場面を進める。</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>親のツッコミフキダシと子どもの無邪気な表情の掛け合い。漫才の間のような構図。</t>
+          <t>連打でゲージを溜めて、必殺技（一気に回収・スーパーダッシュ など）を発動できる</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CD12</t>
+          <t>GM12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>事態の拡大アート</t>
+          <t>ズームのぞき</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ミスや放置のたびに、事態がコミカルに規模を増していく（水たまりが広がる、泡が倍に、ぬいぐるみが山になる など）。拡大も怖くなく、図鑑のように記録される。</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>増えていく事態を図鑑・記録風に並べる。「第2形態」「第3形態」のラベルで笑いに。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CD13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー実況</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ナレーション（ドキュメンタリー風の実況）が大げさに解説する。「ここで、母は気づくのである——」的な重厚テロップで軽い事象を笑う。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー風テロップ（番組ロゴ・字幕）を1コマに添える。重厚演出と軽い内容のギャップ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>仰々しい音響</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ハプニングに大袈裟なBGM・効果音（戦闘開始音・ミステリー調・ファンファーレ）を乗せる。音の重厚さと事象の軽さのギャップで笑う。</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>大袈裟な効果音のオノマトペ（戦闘音・ファンファーレ）を1コマに描き込む。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CD15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>撮影する家族</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>家族の誰かがスマホで撮影していて、リザルト画面で「再生回数」「保存済み」が笑いになる。記録に残る・共有したくなる演出。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>スマホを構える家族を画面端に小さく。「録画中」の表示で笑いに。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CD16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>自信満々宣言</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>冒頭で子ども（または親）が「ぼくならできる!」「まかせて!」と自信満々に宣言し、結果画面で宣言と現実を見比べる。宣言フキダシが笑いの伏線になる。</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>宣言フキダシ（「まかせて!」）を1コマに描き、結果とのギャップを構図で表現。</t>
+          <t>画面の一部を長押しでズームして見られる（まちがい探し・痕跡捜索系と相性が良い）</t>
         </is>
       </c>
     </row>
@@ -5300,7 +6204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5311,247 +6215,369 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>game_text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>illust_text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TW01</t>
+          <t>CD01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ときどき強風（おならの風）がふいて、動きが一瞬止まる</t>
+          <t>得意顔エンド</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>子どもは一切悪気なし。ゲーム内でも最後に子どもが自慢げにドヤ顔ポーズをとり、親も呆れつつ笑って受け入れる演出を入れる。失敗時も罰ではなく「大変なことになった!」のコミカル演出。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>子どもは無邪気で満面のドヤ顔。親は驚きつつも笑顔。子どもが「悪者」に見えない構図。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TW02</t>
+          <t>CD02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>残り10秒でスピードアップするラストスパート演出</t>
+          <t>純粋すぎる一発オチ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>エピソードのオチ（子どもの無邪気な一言・行動）をリザルト画面で大写しにする。子どもの核心を突く一言が一番の見せ場。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>子どもの無邪気な一言（フキダシ）を1コマのオチとして大きく配置。親の反応が顔芸で伝わる構図。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TW03</t>
+          <t>CD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ハテナボックス登場：中身が開くまでわからない</t>
+          <t>破壊力スローモーション</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ハプニングが起こる瞬間（こぼれる・散らかる・脱走開始）を一瞬のスローモーション+ズームで大げさに演出する。ヒットストップと画面シェイクで「事件感」を笑いに変える。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ハプニング発生の瞬間をスローモーション風に切り取る。飛び散るものの軌跡と動きの線で「事件の迫力」を笑いに。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TW04</t>
+          <t>CD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ミスしても1回だけ「お助け再挑戦」（こぼれた牛乳を最後の1滴まで拾いなおす）</t>
+          <t>親の顔芸リアクション</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>親の顔がコミカルに変化する（固まる・のけぞる・回転する・青ざめる）。操作キャラの親の反応芸が画面ジュースの主役。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>親の大げさな表情（顔芸）を1コマの見どころに。子どもの無邪気さとのギャップで笑う構図。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TW05</t>
+          <t>CD05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>コンボ10でオノマトペが画面を駆け巡る大演出</t>
+          <t>勝手に進む子ども</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>操作とは関係なく子ども（またはハプニング源）が勝手に動き出す演出。プレイヤー＝親は「追いつく・止める・回収する」側で、子どもの自由さがゲームの推進力になる。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>自分の世界に入って自由に動く子どもと、それを追いかける親。子どもが主導権を持つ構図。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TW06</t>
+          <t>CD06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>途中から画面がくるっと回る逆さステージ（子ども目線）</t>
+          <t>コミカル物理</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>バウンドする・ヌルヌル滑る・フワフワ浮く・くるくる回るなど、誇張された物理挙動でハプニングの「無茶」を笑えるものにする。現実の危険さは表現しない。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>物理法則を無視したコミカルな動き（浮く・滑る・回る）を静止画でもわかるように。誇張された動きの線。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TW07</t>
+          <t>CD07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ラッキーアイテムを取ると一瞬スローモーション</t>
+          <t>証拠隠滅パロディ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>子どもが無邪気に「証拠」を隠そうとする（笑）パロディ演出。捜索パートやリプレイで犯人の無邪気な行動をムービー風に振り返る。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>「犯人」っぽく構える子どもと、何も知らない純粋な表情のギャップ。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TW08</t>
+          <t>CD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>アイテムがコミカルにバウンドする物理挙動</t>
+          <t>なぜなに純粋顔</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>子どもは「なんで怒られるの?」という純粋な疑問顔。親のツッコミ（フキダシ）と子どもの純粋顔の掛け合いが笑いの軸。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>真顔で純粋な疑問を投げる子どもと、説明を諦めた親。フキダシの掛け合いで笑う構図。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TW09</t>
+          <t>CD09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>連続正解でBGMのテンポがだんだん速くなる</t>
+          <t>ご褒美のハグ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>失敗・成功どちらのエンドでも、最後は親子で笑い合う/ハグする演出で締める。子育ての大変さを「愛おしさ」で受け止める余韻。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>事件の後でも親子が仲良く笑い合う余韻のある構図。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TW10</t>
+          <t>CD10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>途中で2択イベントが挟まる（「助ける? 進む?」など、選択で展開が変わる）</t>
+          <t>無邪気顔ウォッチ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>子どもの無邪気な顔を画面の片隅（または場面内）に大きく常時表示し、状況で表情が変わる。コンボ中=にっこり、ミス=「え?」ときょとん、ピンチ=わくわく照れ顔、リザルト=ドヤ顔。親だけが必死で、子どもは無邪気——この対比が笑いの軸。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>子どもの無邪気で満面な笑顔（またはきょとん顔）を1コマの中心に大きく。親の必死な顔との対比で笑いを生む。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TW11</t>
+          <t>CD11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>途中10秒間は得点2倍のボーナスタイム（画面が虹色に）</t>
+          <t>親のツッコミ漫才</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>親のフキダシツッコミ（「まって」「なんで!?」「きょうは寒いからね…」）が笑いのアクセントになる漫才スタイル。子どもの行動と親のツッコミの掛け合いで場面を進める。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>親のツッコミフキダシと子どもの無邪気な表情の掛け合い。漫才の間のような構図。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TW12</t>
+          <t>CD12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>画面を横切るおじゃまキャラ（飼い犬・ロボ掃除機・園バス など）をタップで退散させられる</t>
+          <t>事態の拡大アート</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ミスや放置のたびに、事態がコミカルに規模を増していく（水たまりが広がる、泡が倍に、ぬいぐるみが山になる など）。拡大も怖くなく、図鑑のように記録される。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>増えていく事態を図鑑・記録風に並べる。「第2形態」「第3形態」のラベルで笑いに。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TW13</t>
+          <t>CD13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ときどき子どもが「手伝ってあげる!」と無邪気なお助けをしかけてくる（助かるのか迷惑なのか）</t>
+          <t>ドキュメンタリー実況</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ナレーション（ドキュメンタリー風の実況）が大げさに解説する。「ここで、母は気づくのである——」的な重厚テロップで軽い事象を笑う。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー風テロップ（番組ロゴ・字幕）を1コマに添える。重厚演出と軽い内容のギャップ。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TW14</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>時間経過で判定帯が縮み、後半ほどシビアになる難易度カーブ</t>
+          <t>仰々しい音響</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ハプニングに大袈裟なBGM・効果音（戦闘開始音・ミステリー調・ファンファーレ）を乗せる。音の重厚さと事象の軽さのギャップで笑う。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>大袈裟な効果音のオノマトペ（戦闘音・ファンファーレ）を1コマに描き込む。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TW15</t>
+          <t>CD15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>連続ミスで「なぜなに純粋顔」イベント：子どもがきょとん顔で復活チャンスをくれる</t>
+          <t>撮影する家族</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>家族の誰かがスマホで撮影していて、リザルト画面で「再生回数」「保存済み」が笑いになる。記録に残る・共有したくなる演出。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>スマホを構える家族を画面端に小さく。「録画中」の表示で笑いに。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TW16</t>
+          <t>CD16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>画面の端に見えにくい隠しボーナスアイテムがある</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TW17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>アイテムが画面の端で跳ね返る（壁バウンド挙動）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TW18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>任意で2倍速モードに挑戦できる（成功すれば得点2倍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TW19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>最後のミスで直前5秒に巻き戻せるリワインド（1回だけ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TW20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>途中で大物（祖父母・ペット・園長先生 など）が登場し、場面が一回変わる</t>
+          <t>自信満々宣言</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>冒頭で子ども（または親）が「ぼくならできる!」「まかせて!」と自信満々に宣言し、結果画面で宣言と現実を見比べる。宣言フキダシが笑いの伏線になる。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>宣言フキダシ（「まかせて!」）を1コマに描き、結果とのギャップを構図で表現。</t>
         </is>
       </c>
     </row>
@@ -5566,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5577,545 +6603,247 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>genre_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>desc</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V_A1</t>
+          <t>TW01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>キャッチ・回収</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>上から落ちてくる／降ってくるものを、エピソードの主役が受け止める・回収する。何をキャッチしどこで受けるかは、必ずエピソードの登場物から決める。</t>
+          <t>ときどき強風（おならの風）がふいて、動きが一瞬止まる</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V_A2</t>
+          <t>TW02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>よけろダッシュ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>主役がエピソードの舞台を進み、障害物を左右によけながらゴール（追跡対象・目的地）を目指す。追いかける・間に合わせたい系のエピソードと相性が良い。主役の乗り物・よけるもの・ゴールはすべてエピソードから決める。</t>
+          <t>残り10秒でスピードアップするラストスパート演出</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V_A3</t>
+          <t>TW03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>スワイプ仕分け</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>流れてくるものを左右スワイプで振り分ける。何が流れ、どこへ振り分けるかは、必ずエピソードの内容から決める。</t>
+          <t>ハテナボックス登場：中身が開くまでわからない</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V_A4</t>
+          <t>TW04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>リズムタップ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>タイミングよくタップする音合わせアクション（「あーん!」のタイミングで口に運ぶ、青信号のタイミングで発進 など）。判定帯が縮むほど難しくなる。タイミングの意味はエピソードから決める。</t>
+          <t>ミスしても1回だけ「お助け再挑戦」（こぼれた牛乳を最後の1滴まで拾いなおす）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V_A5</t>
+          <t>TW05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ねらって発射</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>主役が物を狙って発射・投げて、ターゲットに当てる。角度と強さはドラッグで調整。何を投げ、何を狙うかはエピソードの登場物から決める。</t>
+          <t>コンボ10でオノマトペが画面を駆け巡る大演出</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V_A6</t>
+          <t>TW06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>連打チャージ走行</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>連打で力を溜めて一気にゴールへ向かう連打アクション（背負った子と走り抜く、こぼれる前に駆けつける など）。ゴールの意味はエピソードから決める。</t>
+          <t>途中から画面がくるっと回る逆さステージ（子ども目線）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V_A7</t>
+          <t>TW07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>オートランナー</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>主役が自動で走り、タップでジャンプ・しゃがみして障害物をよけるランナー系。走る場所・よけるものはエピソードから決める。</t>
+          <t>ラッキーアイテムを取ると一瞬スローモーション</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V_A8</t>
+          <t>TW08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>まもりガード</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>流れてくるものから対象（子ども・画面内の誰か）を左右操作でまもるガードアクション。まもるもの・襲ってくるものはエピソードから決める。</t>
+          <t>アイテムがコミカルにバウンドする物理挙動</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V_P1</t>
+          <t>TW09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>仕分け箱</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1問ずつ出るものを2つの箱に振り分ける。箱の意味（食べられる/食べられない など）と中身は、必ずエピソードから決める。</t>
+          <t>連続正解でBGMのテンポがだんだん速くなる</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V_P2</t>
+          <t>TW10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>バランス積み</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>アイテムをぐらぐらの台に積み上げる。台とアイテムは、エピソードの小物に置き換える。</t>
+          <t>途中で2択イベントが挟まる（「助ける? 進む?」など、選択で展開が変わる）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V_P3</t>
+          <t>TW11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>穴うめ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>開いた穴にピースをタイミングよくはめる。穴とピースが何を指すかは、エピソードから決める。</t>
+          <t>途中10秒間は得点2倍のボーナスタイム（画面が虹色に）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V_P4</t>
+          <t>TW12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ならべかえ</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>バラバラになった手順・順番を並び替えるパズル（お風呂の手順、おでかけの支度、事態の再現 など）。手順の意味はエピソードから決める。</t>
+          <t>画面を横切るおじゃまキャラ（飼い犬・ロボ掃除機・園バス など）をタップで退散させられる</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V_P5</t>
+          <t>TW13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>まちがい探し</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2枚のパネルのまちがいを探す。まちがいになる小物はエピソードの登場物から決める。</t>
+          <t>ときどき子どもが「手伝ってあげる!」と無邪気なお助けをしかけてくる（助かるのか迷惑なのか）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V_P6</t>
+          <t>TW14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>かくれ物さがし</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>画面の中に隠れた物・痕跡をタップで探す隠し物パズル（かくれんぼ・痕跡捜索系）。探すもの・隠れる場所はエピソードから決める。</t>
+          <t>時間経過で判定帯が縮み、後半ほどシビアになる難易度カーブ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V_P7</t>
+          <t>TW15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>つなげて消す</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>同じものを3つ以上つなげて消すラインパズル。つなぐ対象はエピソードの登場物から決める。</t>
+          <t>連続ミスで「なぜなに純粋顔」イベント：子どもがきょとん顔で復活チャンスをくれる</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V_P8</t>
+          <t>TW16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>一瞬判断</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>出てくる物を一瞬で「OK/NG」に振り分ける神経パズル（ヒヤリ判定・安全判定 など）。判定の意味はエピソードから決める。</t>
+          <t>画面の端に見えにくい隠しボーナスアイテムがある</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V_M1</t>
+          <t>TW17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>神経衰弱</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>裏返しのカードからペアを探す定番型。カードの絵・ペアの意味は、必ずエピソードの登場物で置き換える。</t>
+          <t>アイテムが画面の端で跳ね返る（壁バウンド挙動）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V_M2</t>
+          <t>TW18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>スピード合わせ</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>出題パネルと同じ絵を選択肢からすばやくタップ。出題内容はエピソードの場面・登場物から決める。</t>
+          <t>任意で2倍速モードに挑戦できる（成功すれば得点2倍）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V_M3</t>
+          <t>TW19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ペア迷路</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>迷路の中でペアになる絵を2枚見つけると扉が開く。迷路のテーマ・絵はエピソードの舞台・登場物にする。</t>
+          <t>最後のミスで直前5秒に巻き戻せるリワインド（1回だけ）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V_M4</t>
+          <t>TW20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>まちがい合わせ</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>出題に対して「まちがっている方」を選ぶ逆転合わせ。油断すると引っかかる。出題内容はエピソードから決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>V_M5</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3枚トリオ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3枚1組のトリオを集める合わせ（朝の支度セット、お風呂セット など）。組の意味はエピソードから決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>V_M6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>覚えて再現</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>一瞬だけ見えた並びを覚えて、同じ並びを再現する記憶合わせ。並びの意味はエピソードから決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>V_M7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>音と絵合わせ</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>効果音・オノマトペと絵を合わせる聴覚合わせ。音の意味はエピソードのフキダシ用オノマトペから決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>V_M8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>G_MATCH</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>カルタ取り</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>流れてくる札の中から、お題に合う札をすばやく取るカルタ風。お題・札はエピソードの登場物から決める。</t>
+          <t>途中で大物（祖父母・ペット・園長先生 など）が登場し、場面が一回変わる</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6141,143 +6869,545 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>genre_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>style_text</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>palette_text</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>texture_text</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>composition_text</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ng_text</t>
+          <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I_GEKIGA</t>
+          <t>V_A1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>昭和劇画調</t>
+          <t>G_ACTION</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>昭和レトロ劇画調の重い描き込み。ハッチング(斜線)による陰影、太く鋭い輪郭線、白黒に近い地にクリムゾンの差し色。大げさな描き込みで「事件感」を笑いに。</t>
+          <t>キャッチ・回収</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>モノクロ基調 + クリムゾンレッド #B3121F / アンバー #E8B500 の差し色</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>斜線ハッチングの網掛け、古い印刷のざらつき感</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>中央に親と子の人物を大きく。背景に放射状の集中線。上部にタイトル帯、フキダシにオノマトペ、下部にエピソード帯。</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>実在人物の似顔絵化はしない(架空の人物として描く)。残虐・不快な表現は避け、あくまで笑いとして描く。</t>
+          <t>上から落ちてくる／降ってくるものを、エピソードの主役が受け止める・回収する。何をキャッチしどこで受けるかは、必ずエピソードの登場物から決める。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I_POP</t>
+          <t>V_A2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>アメコミPOP調</t>
+          <t>G_ACTION</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>アメリカンコミックPOPアート調。ハーフトーン網点、太い黒フチ(3px〜5px)、高彩度。カラフルでポップ、親子どちらにも親しみがある。</t>
+          <t>よけろダッシュ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ビビッドイエロー #FFE500 / シアン #00C2FF / クリムゾンレッド #E8112D / ホワイト #FFFFFF / インクブラック #141414</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ハーフトーン網点(ドットパターン)、レトロ印刷風の質感</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>中央に親と子の人物を大きく、背景に放射状スターバースト。上部にタイトル帯、フキダシにオノマトペ、下部にエピソード帯。</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>実在人物の似顔絵化はしない(架空の人物として描く)。不快な表現は避ける。</t>
+          <t>主役がエピソードの舞台を進み、障害物を左右によけながらゴール（追跡対象・目的地）を目指す。追いかける・間に合わせたい系のエピソードと相性が良い。主役の乗り物・よけるもの・ゴールはすべてエピソードから決める。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I_PHOTO</t>
+          <t>V_A3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>実写風</t>
+          <t>G_ACTION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>実写風の質感(写真風の陰影と奥行き)で「あるある」のリアルさを共感に。柔らかい自然光、浅い被写界深度風のぼかし。人物は擬似写真風(イラスト寄りの実写調)。</t>
+          <t>スワイプ仕分け</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>アースカラー基調(ベージュ/セピア/グレイイエロー)+自然な差し色</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>紙のザラつき(グレイン)、ビネット(周辺減光)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>日常の生活空間を背景に親子を配置。リアルな距離感で、事件の瞬間をスナップショット風に切り取る。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>実在人物の顔写真や似顔絵は使わない(架空人物・後ろ姿・手元中心も可)。不快な表現は避ける。</t>
+          <t>流れてくるものを左右スワイプで振り分ける。何が流れ、どこへ振り分けるかは、必ずエピソードの内容から決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V_A4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G_ACTION</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>リズムタップ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>タイミングよくタップする音合わせアクション（「あーん!」のタイミングで口に運ぶ、青信号のタイミングで発進 など）。判定帯が縮むほど難しくなる。タイミングの意味はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V_A5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G_ACTION</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ねらって発射</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>主役が物を狙って発射・投げて、ターゲットに当てる。角度と強さはドラッグで調整。何を投げ、何を狙うかはエピソードの登場物から決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V_A6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G_ACTION</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>連打チャージ走行</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>連打で力を溜めて一気にゴールへ向かう連打アクション（背負った子と走り抜く、こぼれる前に駆けつける など）。ゴールの意味はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V_A7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G_ACTION</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>オートランナー</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>主役が自動で走り、タップでジャンプ・しゃがみして障害物をよけるランナー系。走る場所・よけるものはエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V_A8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G_ACTION</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>まもりガード</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>流れてくるものから対象（子ども・画面内の誰か）を左右操作でまもるガードアクション。まもるもの・襲ってくるものはエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>V_P1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>仕分け箱</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1問ずつ出るものを2つの箱に振り分ける。箱の意味（食べられる/食べられない など）と中身は、必ずエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>V_P2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>バランス積み</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>アイテムをぐらぐらの台に積み上げる。台とアイテムは、エピソードの小物に置き換える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>V_P3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>穴うめ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>開いた穴にピースをタイミングよくはめる。穴とピースが何を指すかは、エピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>V_P4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ならべかえ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>バラバラになった手順・順番を並び替えるパズル（お風呂の手順、おでかけの支度、事態の再現 など）。手順の意味はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>V_P5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>まちがい探し</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2枚のパネルのまちがいを探す。まちがいになる小物はエピソードの登場物から決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>V_P6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>かくれ物さがし</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>画面の中に隠れた物・痕跡をタップで探す隠し物パズル（かくれんぼ・痕跡捜索系）。探すもの・隠れる場所はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>V_P7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>つなげて消す</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>同じものを3つ以上つなげて消すラインパズル。つなぐ対象はエピソードの登場物から決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>V_P8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>G_PUZZLE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>一瞬判断</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>出てくる物を一瞬で「OK/NG」に振り分ける神経パズル（ヒヤリ判定・安全判定 など）。判定の意味はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>V_M1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>神経衰弱</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>裏返しのカードからペアを探す定番型。カードの絵・ペアの意味は、必ずエピソードの登場物で置き換える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>V_M2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>スピード合わせ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>出題パネルと同じ絵を選択肢からすばやくタップ。出題内容はエピソードの場面・登場物から決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V_M3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ペア迷路</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>迷路の中でペアになる絵を2枚見つけると扉が開く。迷路のテーマ・絵はエピソードの舞台・登場物にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V_M4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>まちがい合わせ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>出題に対して「まちがっている方」を選ぶ逆転合わせ。油断すると引っかかる。出題内容はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V_M5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3枚トリオ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3枚1組のトリオを集める合わせ（朝の支度セット、お風呂セット など）。組の意味はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V_M6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>覚えて再現</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>一瞬だけ見えた並びを覚えて、同じ並びを再現する記憶合わせ。並びの意味はエピソードから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>V_M7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>音と絵合わせ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>効果音・オノマトペと絵を合わせる聴覚合わせ。音の意味はエピソードのフキダシ用オノマトペから決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>V_M8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>カルタ取り</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>流れてくる札の中から、お題に合う札をすばやく取るカルタ風。お題・札はエピソードの登場物から決める。</t>
         </is>
       </c>
     </row>
@@ -6292,7 +7422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6308,198 +7438,138 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>goal_text</t>
+          <t>style_text</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>controls_pc</t>
+          <t>palette_text</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>controls_sp</t>
+          <t>texture_text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>loop_text</t>
+          <t>composition_text</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>score_text</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>win_text</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>lose_text</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>duration_sec</t>
+          <t>ng_text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G_ACTION</t>
+          <t>I_GEKIGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>アクション</t>
+          <t>昭和劇画調</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>落ちてくる・流れてくるものに即反応して、キャッチ/よける/仕分けるシンプルアクション。</t>
+          <t>昭和レトロ劇画調の重い描き込み。ハッチング(斜線)による陰影、太く鋭い輪郭線、白黒に近い地にクリムゾンの差し色。大げさな描き込みで「事件感」を笑いに。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>← → または A D キー、マウスドラッグ</t>
+          <t>モノクロ基調 + クリムゾンレッド #B3121F / アンバー #E8B500 の差し色</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>画面ドラッグ、画面下の左右タッチボタン</t>
+          <t>斜線ハッチングの網掛け、古い印刷のざらつき感</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30〜50秒間、出現ペースがゆっくりから徐々に速くなる。1プレイ30〜50秒でサクッと勝敗が決まる。</t>
+          <t>中央に親と子の人物を大きく。背景に放射状の集中線。上部にタイトル帯、フキダシにオノマトペ、下部にエピソード帯。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>キャッチ+10点×コンボ。ミスでピンチゲージ+12%。</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>タイムアップ時にピンチゲージ100%未満なら成功。</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ピンチゲージが100%に達したら即終了。</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>実在人物の似顔絵化はしない(架空の人物として描く)。残虐・不快な表現は避け、あくまで笑いとして描く。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G_PUZZLE</t>
+          <t>I_POP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>パズル</t>
+          <t>アメコミPOP調</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>あらわれたものを、2つの箱のどちらへ仕分けるか判断するコミカルパズル。</t>
+          <t>アメリカンコミックPOPアート調。ハーフトーン網点、太い黒フチ(3px〜5px)、高彩度。カラフルでポップ、親子どちらにも親しみがある。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>← → キーまたはクリック</t>
+          <t>ビビッドイエロー #FFE500 / シアン #00C2FF / クリムゾンレッド #E8112D / ホワイト #FFFFFF / インクブラック #141414</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>タップ（画面の左半分/右半分）</t>
+          <t>ハーフトーン網点(ドットパターン)、レトロ印刷風の質感</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1問ずつ出題。30〜50秒で何問正解できるか競う。テンポよく、待ち時間なし。</t>
+          <t>中央に親と子の人物を大きく、背景に放射状スターバースト。上部にタイトル帯、フキダシにオノマトペ、下部にエピソード帯。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>正解+12点×コンボ。はずれでピンチゲージ+10%。</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>タイムアップ時の正解数とピンチゲージで判定。</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ピンチゲージ100%で即終了。</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>実在人物の似顔絵化はしない(架空の人物として描く)。不快な表現は避ける。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G_MATCH</t>
+          <t>I_PHOTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>絵合わせ</t>
+          <t>実写風</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>カードをめくって同じ絵をそろえる神経衰弱。位置を覚える力が勝負。</t>
+          <t>実写風の質感(写真風の陰影と奥行き)で「あるある」のリアルさを共感に。柔らかい自然光、浅い被写界深度風のぼかし。人物は擬似写真風(イラスト寄りの実写調)。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>クリックでカードをめくる</t>
+          <t>アースカラー基調(ベージュ/セピア/グレイイエロー)+自然な差し色</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>タップでカードをめくる</t>
+          <t>紙のザラつき(グレイン)、ビネット(周辺減光)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5組そろえるか、制限時間50秒。待ち時間なしのテンポ重視。</t>
+          <t>日常の生活空間を背景に親子を配置。リアルな距離感で、事件の瞬間をスナップショット風に切り取る。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ペア成立+15点×コンボ。はずれでピンチゲージ+6%。</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5組そろえきったら成功（残り時間ボーナス）。</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ピンチゲージ100%で即終了。</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>実在人物の顔写真や似顔絵は使わない(架空人物・後ろ姿・手元中心も可)。不快な表現は避ける。</t>
         </is>
       </c>
     </row>
@@ -6514,7 +7584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6530,131 +7600,198 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>style_text</t>
+          <t>goal_text</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>palette_text</t>
+          <t>controls_pc</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>font_text</t>
+          <t>controls_sp</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>bg_text</t>
+          <t>loop_text</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>effect_text</t>
+          <t>score_text</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>bgm_text</t>
+          <t>win_text</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>se_text</t>
+          <t>lose_text</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>duration_sec</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T_POP</t>
+          <t>G_ACTION</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>アメコミPOP風</t>
+          <t>アクション</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ベンデイドット・ハーフトーン網点を背景・オブジェクトに適用。太い黒フチ(solid 3px〜5px)、強烈なコントラスト、高彩度の配色。レトロコミック・ヴィンテージ印刷風の質感や枠線。</t>
+          <t>落ちてくる・流れてくるものに即反応して、キャッチ/よける/仕分けるシンプルアクション。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>シアン #00C2FF / ビビッドイエロー #FFE500 / クリムゾンレッド #E8112D / ホワイト #FFFFFF / インクブラック #141414</t>
+          <t>← → または A D キー、マウスドラッグ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>丸ゴシック系の太字(例: 'M PLUS Rounded 1c','Hiragino Maru Gothic ProN','Yu Gothic')。タイトルは少し傾けて配置。</t>
+          <t>画面ドラッグ、画面下の左右タッチボタン</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ハーフトーン網点(ドットパターン)の背景 + 紙のような温かい地色</t>
+          <t>30〜50秒間、出現ペースがゆっくりから徐々に速くなる。1プレイ30〜50秒でサクッと勝敗が決まる。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ギザギザのコミック風フキダシ(OOPS!/EMERGENCY!/WHAT!?/CATCH!)が画面に飛び出す演出。ヒット・ピンチ時の画面全体シェイク、スターバースト衝撃線、星・汗・水滴のパーティクル放出。コンボ・重要イベント時に一瞬のヒットストップ(数フレーム)とズーム。</t>
+          <t>キャッチ+10点×コンボ。ミスでピンチゲージ+12%。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>レトロファンク風のベースライン+アルペジオメロディのアップテンポBGM(128bpm相当)を、Web Audio APIのタイマー/シーケンサーで自動演奏。START操作時にAudioContextを安全に初期化・アンミュートして即時再生。タイトル画面とリザルト画面はジングル/BGMを切り替え。画面内にBGMのON/OFFトグルを設置。</t>
+          <t>タイムアップ時にピンチゲージ100%未満なら成功。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>成功音=小気味よいピッチ上昇・ファンファーレ / 失敗・衝突音=濁ったノイズ+ピッチ下降 / 警告音=ピンチゲージ80%以上でのリズミカルな警報アラート / アクション音=ボタンクリック、スライド、ダッシュ。</t>
+          <t>ピンチゲージが100%に達したら即終了。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T_PIXEL</t>
+          <t>G_PUZZLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16ビットドットスタイル</t>
+          <t>パズル</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16ビット時代のドット絵グラフィック。チェッカー状のピクセルパターン背景。滑らかなグラデーションを避け、ピクセル感を保つ。レトロ家庭用ゲーム機風のベゼル枠。</t>
+          <t>あらわれたものを、2つの箱のどちらへ仕分けるか判断するコミカルパズル。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>レトログリーン #3EE6C1 / ミッドナイトブルー #101828 / サンイエロー #FFD23F / コーラルピンク #FF5D8F / ホワイト #F4F4F4</t>
+          <t>← → キーまたはクリック</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ピクセル/等幅フォント(例: 'Courier New', monospace)。8bit風タイポ。数字は桁を揃える。</t>
+          <t>タップ（画面の左半分/右半分）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ピクセルパターン背景 + CRT風の走査線(任意)</t>
+          <t>1問ずつ出題。30〜50秒で何問正解できるか競う。テンポよく、待ち時間なし。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8bit風の爆発エフェクト(ピクセル粒子・星型スプライト)。画面シェイク、ヒットストップ、コンボ時ズーム。フキダシは角ばった8bit風の枠(OOPS!/EMERGENCY!/WHAT!?)。</t>
+          <t>正解+12点×コンボ。はずれでピンチゲージ+10%。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>チップチューン風BGM(150bpm相当・スクエアウェーブ中心)をWeb Audio APIでシーケンサー自動演奏。START操作時にAudioContextを安全に初期化。タイトル/リザルトでジングル切替。BGM ON/OFFトグルを設置。</t>
+          <t>タイムアップ時の正解数とピンチゲージで判定。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>成功音=上昇アルペジオ / 失敗音=下降ノイズ / 警告音=警報ビープ / アクション音=ブリップ音。</t>
+          <t>ピンチゲージ100%で即終了。</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>G_MATCH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>絵合わせ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>カードをめくって同じ絵をそろえる神経衰弱。位置を覚える力が勝負。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>クリックでカードをめくる</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>タップでカードをめくる</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5組そろえるか、制限時間50秒。待ち時間なしのテンポ重視。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ペア成立+15点×コンボ。はずれでピンチゲージ+6%。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5組そろえきったら成功（残り時間ボーナス）。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ピンチゲージ100%で即終了。</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
     </row>
